--- a/results.xlsx
+++ b/results.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -437,17 +437,32 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>RMSE</t>
+          <t>CV RMSE</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>MAE</t>
+          <t>CV MAE</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>R²</t>
+          <t>CV R²</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Test RMSE</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Test MAE</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Test R²</t>
         </is>
       </c>
     </row>
@@ -458,13 +473,22 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.129445433616638</v>
+        <v>1.280116248130798</v>
       </c>
       <c r="C2" t="n">
-        <v>0.8544966578483582</v>
+        <v>0.9479066967964173</v>
       </c>
       <c r="D2" t="n">
-        <v>0.6960899233818054</v>
+        <v>0.6096819400787353</v>
+      </c>
+      <c r="E2" t="n">
+        <v>1.165900111198425</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.8638843297958374</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.712158203125</v>
       </c>
     </row>
     <row r="3">
@@ -474,13 +498,22 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.8766000866889954</v>
+        <v>0.8135337114334107</v>
       </c>
       <c r="C3" t="n">
-        <v>0.6947675943374634</v>
+        <v>0.6158104419708252</v>
       </c>
       <c r="D3" t="n">
-        <v>0.816929817199707</v>
+        <v>0.8442302227020264</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0.8848539590835571</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.6811050176620483</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.8342038989067078</v>
       </c>
     </row>
     <row r="4">
@@ -490,13 +523,22 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.7397935390472412</v>
+        <v>0.9344895124435425</v>
       </c>
       <c r="C4" t="n">
-        <v>0.5490907430648804</v>
+        <v>0.6745546579360961</v>
       </c>
       <c r="D4" t="n">
-        <v>0.8696126341819763</v>
+        <v>0.7929173827171325</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.8037866950035095</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.5944371223449707</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.8631916046142578</v>
       </c>
     </row>
   </sheetData>
@@ -510,7 +552,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E115"/>
+  <dimension ref="A1:E226"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -543,2167 +585,4276 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cc3ccnc4N(C1CC1)c2ncccc2C(=O)Nc34 </t>
+          <t>Brc1ccccc1Br</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>-3.190000057220459</v>
+        <v>-3.5</v>
       </c>
       <c r="C2" t="n">
-        <v>-4.958326816558838</v>
+        <v>-3.129695653915405</v>
       </c>
       <c r="D2" t="n">
-        <v>-3.257460117340088</v>
+        <v>-3.455044031143188</v>
       </c>
       <c r="E2" t="n">
-        <v>-3.604706048965454</v>
+        <v>-3.156476020812988</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>COC(=O)c1ccccc1</t>
+          <t xml:space="preserve">CCC1(C(C)C)C(=O)NC(=O)NC1=O </t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-1.850000023841858</v>
+        <v>-2.210000038146973</v>
       </c>
       <c r="C3" t="n">
-        <v>-1.60979437828064</v>
+        <v>-2.237829923629761</v>
       </c>
       <c r="D3" t="n">
-        <v>-1.037907600402832</v>
+        <v>-1.361950397491455</v>
       </c>
       <c r="E3" t="n">
-        <v>-1.64836573600769</v>
+        <v>-2.339644193649292</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>CC(C)Br</t>
+          <t>CC(C)COC(=O)C</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>-1.590000033378601</v>
+        <v>-1.210000038146973</v>
       </c>
       <c r="C4" t="n">
-        <v>-1.766840934753418</v>
+        <v>-0.5418119430541992</v>
       </c>
       <c r="D4" t="n">
-        <v>-2.116953134536743</v>
+        <v>-0.5427730679512024</v>
       </c>
       <c r="E4" t="n">
-        <v>-1.353154301643372</v>
+        <v>-1.579140901565552</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>C=CCCC=C</t>
+          <t xml:space="preserve">Clc1cccc(Cl)c1c2ccccc2 </t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-2.680000066757202</v>
+        <v>-5.210000038146973</v>
       </c>
       <c r="C5" t="n">
-        <v>-2.31112265586853</v>
+        <v>-6.49118185043335</v>
       </c>
       <c r="D5" t="n">
-        <v>-2.327693462371826</v>
+        <v>-4.783836841583252</v>
       </c>
       <c r="E5" t="n">
-        <v>-2.488356113433838</v>
+        <v>-4.775817394256592</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>CN(C)C(=O)Nc1ccc(Cl)c(Cl)c1</t>
+          <t>CC1(C)C(C=C(Cl)C(F)(F)F)C1C(=O)OC(C#N)c2cccc(Oc3ccccc3)c2</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-3.799999952316284</v>
+        <v>-8.175999641418457</v>
       </c>
       <c r="C6" t="n">
-        <v>-3.281651258468628</v>
+        <v>-8.240293502807617</v>
       </c>
       <c r="D6" t="n">
-        <v>-3.154874324798584</v>
+        <v>-6.649898529052734</v>
       </c>
       <c r="E6" t="n">
-        <v>-3.44815468788147</v>
+        <v>-7.255655765533447</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>O=C1NC(=O)NC(=O)C1(CC=C)c1ccccc1</t>
+          <t xml:space="preserve">CC(=O)C3CCC4C2CC=C1CC(O)CCC1(C)C2CCC34C </t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>-2.36899995803833</v>
+        <v>-4.650000095367432</v>
       </c>
       <c r="C7" t="n">
-        <v>-2.018640041351318</v>
+        <v>-4.67878532409668</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.88393247127533</v>
+        <v>-3.948612451553345</v>
       </c>
       <c r="E7" t="n">
-        <v>-2.392404317855835</v>
+        <v>-4.54561710357666</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t xml:space="preserve">NS(=O)(=O)c2cc1c(NC(NS1(=O)=O)C(Cl)Cl)cc2Cl </t>
+          <t>CN(C)C(=O)Nc1ccccc1</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-2.680000066757202</v>
+        <v>-1.600000023841858</v>
       </c>
       <c r="C8" t="n">
-        <v>-4.283108711242676</v>
+        <v>-3.010938405990601</v>
       </c>
       <c r="D8" t="n">
-        <v>-3.030840635299683</v>
+        <v>-1.37623143196106</v>
       </c>
       <c r="E8" t="n">
-        <v>-3.354293346405029</v>
+        <v>-2.179249048233032</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>ClCc1ccccc1</t>
+          <t xml:space="preserve">NC(=N)NS(=O)(=O)c1ccc(N)cc1 </t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-2.390000104904175</v>
+        <v>-1.990000009536743</v>
       </c>
       <c r="C9" t="n">
-        <v>-3.829021215438843</v>
+        <v>-2.365668773651123</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.391813516616821</v>
+        <v>-2.337333917617798</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.881724119186401</v>
+        <v>-1.599374413490295</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>C/C=C/C=O</t>
+          <t>Nc2cnn(c1ccccc1)c(=O)c2Cl</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.3199999928474426</v>
+        <v>-2.878000020980835</v>
       </c>
       <c r="C10" t="n">
-        <v>-1.140222787857056</v>
+        <v>-3.042974472045898</v>
       </c>
       <c r="D10" t="n">
-        <v>0.71372389793396</v>
+        <v>-2.293567419052124</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.2571670413017273</v>
+        <v>-2.474918127059937</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>CCC#CCC</t>
+          <t>Oc1cc(Cl)c(Cl)cc1Cl</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>-1.990000009536743</v>
+        <v>-2.210000038146973</v>
       </c>
       <c r="C11" t="n">
-        <v>-2.006701469421387</v>
+        <v>-1.258082151412964</v>
       </c>
       <c r="D11" t="n">
-        <v>0.4026242792606354</v>
+        <v>-2.562128067016602</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.9098514914512634</v>
+        <v>-2.769645690917969</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t xml:space="preserve">CCCCc1c(C)nc(NCC)nc1OS(=O)(=O)N(C)C </t>
+          <t xml:space="preserve">CC1=CC(=O)CC(C)(C)C1 </t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>-4.159999847412109</v>
+        <v>-1.059999942779541</v>
       </c>
       <c r="C12" t="n">
-        <v>-2.974610090255737</v>
+        <v>-3.392359972000122</v>
       </c>
       <c r="D12" t="n">
-        <v>-3.436829566955566</v>
+        <v>-0.7793754935264587</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.599576234817505</v>
+        <v>-1.183547854423523</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>CC(C)CC(=O)C</t>
+          <t>Cc1ccc2cc3ccccc3cc2c1</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>-0.7400000095367432</v>
+        <v>-6.960000038146973</v>
       </c>
       <c r="C13" t="n">
-        <v>-0.7675204277038574</v>
+        <v>-6.603367805480957</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.4199466407299042</v>
+        <v>-5.978716850280762</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.8826068043708801</v>
+        <v>-6.897336006164551</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>O=C1NC(=O)NC(=O)C1(CC)C(C)C</t>
+          <t>CCCCCCOC(=O)c1ccccc1C(=O)OCCCCCC</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>-2.148000001907349</v>
+        <v>-6.144000053405762</v>
       </c>
       <c r="C14" t="n">
-        <v>-2.231376886367798</v>
+        <v>-5.023574352264404</v>
       </c>
       <c r="D14" t="n">
-        <v>-1.43697988986969</v>
+        <v>-4.310651302337646</v>
       </c>
       <c r="E14" t="n">
-        <v>-1.988650321960449</v>
+        <v>-4.775411128997803</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>CC(C)C</t>
+          <t>NC(=O)c1cnccn1</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>-2.549999952316284</v>
+        <v>-0.6669999957084656</v>
       </c>
       <c r="C15" t="n">
-        <v>-1.407312154769897</v>
+        <v>-0.4490694999694824</v>
       </c>
       <c r="D15" t="n">
-        <v>-2.71044921875</v>
+        <v>0.993121325969696</v>
       </c>
       <c r="E15" t="n">
-        <v>-3.334912776947021</v>
+        <v>0.9974968433380127</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>O=N(=O)c1c(Cl)c(Cl)ccc1</t>
+          <t>CC=CC=O</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>-3.480000019073486</v>
+        <v>0.3199999928474426</v>
       </c>
       <c r="C16" t="n">
-        <v>-3.161296606063843</v>
+        <v>-0.7571551203727722</v>
       </c>
       <c r="D16" t="n">
-        <v>-2.813152551651001</v>
+        <v>1.073553323745728</v>
       </c>
       <c r="E16" t="n">
-        <v>-3.784727573394775</v>
+        <v>0.3280182778835297</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">CC5(C)OC4CC3C2CCC1=CC(=O)C=CC1(C)C2(F)C(O)CC3(C)C4(O5)C(=O)CO </t>
+          <t>Oc1ccccc1O</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>-4.309999942779541</v>
+        <v>0.6200000047683716</v>
       </c>
       <c r="C17" t="n">
-        <v>-2.373477220535278</v>
+        <v>-1.387372970581055</v>
       </c>
       <c r="D17" t="n">
-        <v>-3.174429178237915</v>
+        <v>-0.3328573107719421</v>
       </c>
       <c r="E17" t="n">
-        <v>-3.75072193145752</v>
+        <v>-0.4492541253566742</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">CC34CC(O)C1(F)C(CCC2=CC(=O)CCC12C)C3CCC4(O)C(=O)CO </t>
+          <t>CC(C)C(C(=O)OC(C#N)c1cccc(Oc2ccccc2)c1)c3ccc(OC(F)F)cc3</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>-3.430000066757202</v>
+        <v>-6.875999927520752</v>
       </c>
       <c r="C18" t="n">
-        <v>-3.049989938735962</v>
+        <v>-5.318087100982666</v>
       </c>
       <c r="D18" t="n">
-        <v>-3.016270637512207</v>
+        <v>-6.867051124572754</v>
       </c>
       <c r="E18" t="n">
-        <v>-3.731913328170776</v>
+        <v>-6.952692031860352</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>CC(C)O</t>
+          <t>CCOP(=S)(OCC)Oc1cc(C)nc(n1)C(C)C</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.4300000071525574</v>
+        <v>-3.640000104904175</v>
       </c>
       <c r="C19" t="n">
-        <v>0.02492660284042358</v>
+        <v>-3.25118088722229</v>
       </c>
       <c r="D19" t="n">
-        <v>1.41465950012207</v>
+        <v>-3.142481565475464</v>
       </c>
       <c r="E19" t="n">
-        <v>1.356851100921631</v>
+        <v>-3.304226636886597</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>O=C(c1ccccc1)c2ccccc2</t>
+          <t xml:space="preserve">CCN2c1nc(Cl)ccc1N(C)C(=O)c3cccnc23 </t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>-3.119999885559082</v>
+        <v>-4.113999843597412</v>
       </c>
       <c r="C20" t="n">
-        <v>-1.876093626022339</v>
+        <v>-3.700246095657349</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.814883947372437</v>
+        <v>-3.507876634597778</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.865703344345093</v>
+        <v>-4.348254680633545</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>CC(C)(C)C(=O)C(Oc1ccc(Cl)cc1)n2cncn2</t>
+          <t>CC(C)COC=O</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>-3.609999895095825</v>
+        <v>-1.009999990463257</v>
       </c>
       <c r="C21" t="n">
-        <v>-2.640374898910522</v>
+        <v>-1.28021776676178</v>
       </c>
       <c r="D21" t="n">
-        <v>-4.30411958694458</v>
+        <v>-0.841538667678833</v>
       </c>
       <c r="E21" t="n">
-        <v>-3.901829719543457</v>
+        <v>-1.354011297225952</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>CCCN(CCC)c1c(cc(cc1N(=O)=O)C(F)(F)F)N(=O)=O</t>
+          <t>CCC(C)CO</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>-5.679999828338623</v>
+        <v>-0.4699999988079071</v>
       </c>
       <c r="C22" t="n">
-        <v>-5.955467224121094</v>
+        <v>-0.3877916634082794</v>
       </c>
       <c r="D22" t="n">
-        <v>-5.539226531982422</v>
+        <v>-0.6713961362838745</v>
       </c>
       <c r="E22" t="n">
-        <v>-6.661869049072266</v>
+        <v>-0.4569856822490692</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Oc1ccc(Br)cc1</t>
+          <t>Cc1ccc2ccccc2c1</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>-1.090000033378601</v>
+        <v>-3.769999980926514</v>
       </c>
       <c r="C23" t="n">
-        <v>-1.729309797286987</v>
+        <v>-4.602106094360352</v>
       </c>
       <c r="D23" t="n">
-        <v>-1.939767241477966</v>
+        <v>-3.873131036758423</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.802809596061707</v>
+        <v>-4.504860877990723</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>c1ccc2c(c1)cc3ccc4cccc5ccc2c3c45</t>
+          <t>OCc1ccccc1</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>-8.699000358581543</v>
+        <v>-0.4000000059604645</v>
       </c>
       <c r="C24" t="n">
-        <v>-8.458724975585938</v>
+        <v>-2.452057123184204</v>
       </c>
       <c r="D24" t="n">
-        <v>-6.952995777130127</v>
+        <v>-0.6600528359413147</v>
       </c>
       <c r="E24" t="n">
-        <v>-8.121772766113281</v>
+        <v>-0.115552045404911</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>COc1ccccc1Cl</t>
+          <t>CCOC(=O)c1cncn1C(C)c2ccccc2</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>-2.460000038146973</v>
+        <v>-4.735000133514404</v>
       </c>
       <c r="C25" t="n">
-        <v>-2.80930495262146</v>
+        <v>-1.57300853729248</v>
       </c>
       <c r="D25" t="n">
-        <v>-1.889399528503418</v>
+        <v>-2.787085294723511</v>
       </c>
       <c r="E25" t="n">
-        <v>-2.094413042068481</v>
+        <v>-2.718212604522705</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>CCCCCCCCC=C</t>
+          <t>c1ccc2ncccc2c1</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>-5.510000228881836</v>
+        <v>-1.299999952316284</v>
       </c>
       <c r="C26" t="n">
-        <v>-5.090243816375732</v>
+        <v>-3.140897035598755</v>
       </c>
       <c r="D26" t="n">
-        <v>-5.555148601531982</v>
+        <v>-2.075997591018677</v>
       </c>
       <c r="E26" t="n">
-        <v>-5.571683406829834</v>
+        <v>-2.237616062164307</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>CCNc1ccccc1</t>
+          <t xml:space="preserve">CCCC1C(=O)N3N(C1=O)c2cc(C)ccc2N=C3N(C)C </t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>-1.700000047683716</v>
+        <v>-3.538000106811523</v>
       </c>
       <c r="C27" t="n">
-        <v>-1.532541513442993</v>
+        <v>-4.002769947052002</v>
       </c>
       <c r="D27" t="n">
-        <v>-2.001879215240479</v>
+        <v>-2.672681093215942</v>
       </c>
       <c r="E27" t="n">
-        <v>-2.265169620513916</v>
+        <v>-3.544888496398926</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Cc1ccccc1Br</t>
+          <t>O=C1NC(=O)NC(=O)C1(CC)C(C)CC</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-2.230000019073486</v>
+        <v>-2.390000104904175</v>
       </c>
       <c r="C28" t="n">
-        <v>-2.857717275619507</v>
+        <v>-2.270833015441895</v>
       </c>
       <c r="D28" t="n">
-        <v>-2.636647462844849</v>
+        <v>-1.416238069534302</v>
       </c>
       <c r="E28" t="n">
-        <v>-3.145651340484619</v>
+        <v>-2.261245250701904</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>CCCOC(C)C</t>
+          <t>CSCS(=O)CC(CO)NC(=O)C=Cc1c(C)[nH]c(=O)[nH]c1=O</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-1.340000033378601</v>
+        <v>-1.980999946594238</v>
       </c>
       <c r="C29" t="n">
-        <v>-1.680883646011353</v>
+        <v>-1.650170564651489</v>
       </c>
       <c r="D29" t="n">
-        <v>-1.641009926795959</v>
+        <v>-1.361279487609863</v>
       </c>
       <c r="E29" t="n">
-        <v>-0.9248961806297302</v>
+        <v>-1.174729943275452</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>CCCCC(CC)C=O</t>
+          <t>C=CC#N</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-2.130000114440918</v>
+        <v>0.1500000059604645</v>
       </c>
       <c r="C30" t="n">
-        <v>-3.08551812171936</v>
+        <v>-1.017109632492065</v>
       </c>
       <c r="D30" t="n">
-        <v>-2.263626098632812</v>
+        <v>0.5253790020942688</v>
       </c>
       <c r="E30" t="n">
-        <v>-2.393193244934082</v>
+        <v>1.269315838813782</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>BrCCBr</t>
+          <t>c1ccc(cc1)c2ccccc2</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-1.679999947547913</v>
+        <v>-4.34499979019165</v>
       </c>
       <c r="C31" t="n">
-        <v>-1.119418144226074</v>
+        <v>-6.371237754821777</v>
       </c>
       <c r="D31" t="n">
-        <v>-1.649738430976868</v>
+        <v>-3.184842824935913</v>
       </c>
       <c r="E31" t="n">
-        <v>-1.685905814170837</v>
+        <v>-3.513191699981689</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t xml:space="preserve">OCC3OC(OCC2OC(OC(C#N)c1ccccc1)C(O)C(O)C2O)C(O)C(O)C3O </t>
+          <t>CC=C(C)C</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-0.7699999809265137</v>
+        <v>-2.559999942779541</v>
       </c>
       <c r="C32" t="n">
-        <v>-1.047260999679565</v>
+        <v>-0.04959729313850403</v>
       </c>
       <c r="D32" t="n">
-        <v>-2.099374532699585</v>
+        <v>-1.654616594314575</v>
       </c>
       <c r="E32" t="n">
-        <v>-3.023037672042847</v>
+        <v>-1.724758982658386</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>CCCCCl</t>
+          <t>CC(=C)C1CC=C(C)C(=O)C1</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-2.029999971389771</v>
+        <v>-2.059999942779541</v>
       </c>
       <c r="C33" t="n">
-        <v>-2.004945278167725</v>
+        <v>-3.362271070480347</v>
       </c>
       <c r="D33" t="n">
-        <v>-1.701585531234741</v>
+        <v>-2.17363715171814</v>
       </c>
       <c r="E33" t="n">
-        <v>-2.089868545532227</v>
+        <v>-3.547316789627075</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>O=N(=O)c1cc(cc(c1)N(=O)=O)N(=O)=O</t>
+          <t>O=C1CCC(=O)N1</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-2.890000104904175</v>
+        <v>0.300000011920929</v>
       </c>
       <c r="C34" t="n">
-        <v>-3.167951345443726</v>
+        <v>-0.562909722328186</v>
       </c>
       <c r="D34" t="n">
-        <v>-1.918605804443359</v>
+        <v>1.826337337493896</v>
       </c>
       <c r="E34" t="n">
-        <v>-2.6297287940979</v>
+        <v>1.002820372581482</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t xml:space="preserve">CC1=C(CCCO1)C(=O)Nc2ccccc2 </t>
+          <t xml:space="preserve">CC34CCC1C(CCc2cc(O)ccc12)C3CC(O)C4O </t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-2.559999942779541</v>
+        <v>-4.954999923706055</v>
       </c>
       <c r="C35" t="n">
-        <v>-2.750136375427246</v>
+        <v>-5.440972805023193</v>
       </c>
       <c r="D35" t="n">
-        <v>-2.976536273956299</v>
+        <v>-4.024680614471436</v>
       </c>
       <c r="E35" t="n">
-        <v>-3.443961381912231</v>
+        <v>-4.512533664703369</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>CCCC1COC(Cn2cncn2)(O1)c3ccc(Cl)cc3Cl</t>
+          <t>OCC1OC(O)C(O)C(O)C1O</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-3.493000030517578</v>
+        <v>0.7400000095367432</v>
       </c>
       <c r="C36" t="n">
-        <v>-3.547532558441162</v>
+        <v>0.1976569294929504</v>
       </c>
       <c r="D36" t="n">
-        <v>-2.058396100997925</v>
+        <v>0.5163999199867249</v>
       </c>
       <c r="E36" t="n">
-        <v>-3.30029821395874</v>
+        <v>0.3207263052463531</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Cc1cccc(C)c1</t>
+          <t>Clc1cc(c(Cl)c(Cl)c1Cl)c2cc(Cl)c(Cl)c(Cl)c2Cl</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>-2.819999933242798</v>
+        <v>-9.159999847412109</v>
       </c>
       <c r="C37" t="n">
-        <v>-3.18477988243103</v>
+        <v>-7.440655708312988</v>
       </c>
       <c r="D37" t="n">
-        <v>-1.749271869659424</v>
+        <v>-9.068751335144043</v>
       </c>
       <c r="E37" t="n">
-        <v>-2.997464656829834</v>
+        <v>-8.851675033569336</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>CCCCCCCl</t>
+          <t>C1(=O)NC(=O)NC(=O)C1(O)C2(O)C(=O)NC(=O)NC2(=O)</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>-3.119999885559082</v>
+        <v>-1.990000009536743</v>
       </c>
       <c r="C38" t="n">
-        <v>-3.939862728118896</v>
+        <v>-1.309115886688232</v>
       </c>
       <c r="D38" t="n">
-        <v>-3.374544858932495</v>
+        <v>-0.8508198857307434</v>
       </c>
       <c r="E38" t="n">
-        <v>-3.720590353012085</v>
+        <v>-3.165551662445068</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>CCCCC(=O)OCC</t>
+          <t>Fc1cccc(F)c1</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>-2.25</v>
+        <v>-2</v>
       </c>
       <c r="C39" t="n">
-        <v>-1.536878347396851</v>
+        <v>-1.713895320892334</v>
       </c>
       <c r="D39" t="n">
-        <v>-1.31279182434082</v>
+        <v>-3.001729249954224</v>
       </c>
       <c r="E39" t="n">
-        <v>-1.727789044380188</v>
+        <v>-2.410296440124512</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>CC34CCc1c(ccc2cc(O)ccc12)C3CCC4=O</t>
+          <t>Cc1cc(=O)n(c2ccccc2)n1C</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>-5.239999771118164</v>
+        <v>0.7149999737739563</v>
       </c>
       <c r="C40" t="n">
-        <v>-3.784410238265991</v>
+        <v>-2.771745204925537</v>
       </c>
       <c r="D40" t="n">
-        <v>-4.314857959747314</v>
+        <v>-0.7230273485183716</v>
       </c>
       <c r="E40" t="n">
-        <v>-4.981057643890381</v>
+        <v>-1.014973521232605</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t xml:space="preserve">COc2cc1c(N)nc(nc1c(OC)c2OC)N3CCN(CC3)C(=O)OCC(C)(C)O </t>
+          <t>CCNc1nc(NC(C)(C)C)nc(SC)n1</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>-3.638000011444092</v>
+        <v>-4</v>
       </c>
       <c r="C41" t="n">
-        <v>-3.445669174194336</v>
+        <v>-3.781432151794434</v>
       </c>
       <c r="D41" t="n">
-        <v>-1.563758134841919</v>
+        <v>-3.584523439407349</v>
       </c>
       <c r="E41" t="n">
-        <v>-2.300518989562988</v>
+        <v>-3.874207019805908</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t xml:space="preserve">COc1ncnc2nccnc12 </t>
+          <t>C1OC(O)C(O)C(O)C1O</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>-1.110000014305115</v>
+        <v>0.3899999856948853</v>
       </c>
       <c r="C42" t="n">
-        <v>-0.8155143260955811</v>
+        <v>-1.244336843490601</v>
       </c>
       <c r="D42" t="n">
-        <v>-0.6758008599281311</v>
+        <v>0.4843056797981262</v>
       </c>
       <c r="E42" t="n">
-        <v>-0.7756720185279846</v>
+        <v>0.9944838285446167</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Cc1ccc(C)c(C)c1</t>
+          <t>CNC(=O)ON=C(SC)C(=O)N(C)C</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>-3.309999942779541</v>
+        <v>0.1059999987483025</v>
       </c>
       <c r="C43" t="n">
-        <v>-3.822434186935425</v>
+        <v>0.07307291030883789</v>
       </c>
       <c r="D43" t="n">
-        <v>-2.668256044387817</v>
+        <v>-1.235599279403687</v>
       </c>
       <c r="E43" t="n">
-        <v>-3.530725955963135</v>
+        <v>0.1709984838962555</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>CCOC(=O)CC</t>
+          <t xml:space="preserve">CCCCOC(=O)c1ccccc1C(=O)OCCCC </t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>-0.6600000262260437</v>
+        <v>-4.400000095367432</v>
       </c>
       <c r="C44" t="n">
-        <v>-0.5121091604232788</v>
+        <v>-3.521554946899414</v>
       </c>
       <c r="D44" t="n">
-        <v>0.6965816020965576</v>
+        <v>-3.523591995239258</v>
       </c>
       <c r="E44" t="n">
-        <v>0.3811638951301575</v>
+        <v>-3.844103097915649</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t xml:space="preserve">O2c1ccc(N)cc1N(C)C(=O)c3cc(C)ccc23 </t>
+          <t>CC(C)C(O)C(C)C</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>-3.927999973297119</v>
+        <v>-1.220000028610229</v>
       </c>
       <c r="C45" t="n">
-        <v>-2.630140542984009</v>
+        <v>-0.1232308447360992</v>
       </c>
       <c r="D45" t="n">
-        <v>-3.179449319839478</v>
+        <v>-1.733081340789795</v>
       </c>
       <c r="E45" t="n">
-        <v>-3.599257946014404</v>
+        <v>-1.318957924842834</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t xml:space="preserve">CC4CC3C2CCC1=CC(=O)C=CC1(C)C2(F)C(O)CC3(C)C4(O)C(=O)COC(C)=O </t>
+          <t>CCC(C)(O)CC</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>-4.900000095367432</v>
+        <v>-0.3600000143051147</v>
       </c>
       <c r="C46" t="n">
-        <v>-4.478627681732178</v>
+        <v>-0.4555911123752594</v>
       </c>
       <c r="D46" t="n">
-        <v>-3.756707668304443</v>
+        <v>-0.2662609815597534</v>
       </c>
       <c r="E46" t="n">
-        <v>-5.025634288787842</v>
+        <v>-0.7332462072372437</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>c1ccccc1n2ncc(N)c(Br)c2(=O)</t>
+          <t xml:space="preserve">COC(=O)c1cccnc1 </t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>-3.127000093460083</v>
+        <v>-0.4600000083446503</v>
       </c>
       <c r="C47" t="n">
-        <v>-1.342813014984131</v>
+        <v>-0.6283909678459167</v>
       </c>
       <c r="D47" t="n">
-        <v>-1.750437259674072</v>
+        <v>0.227969229221344</v>
       </c>
       <c r="E47" t="n">
-        <v>-3.081624507904053</v>
+        <v>-0.4048262536525726</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Oc1ccc(Cl)cc1C(=O)Nc2ccc(cc2Cl)N(=O)=O</t>
+          <t>CC=C(C(=CC)c1ccc(O)cc1)c2ccc(O)cc2</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>-4.699999809265137</v>
+        <v>-4.949999809265137</v>
       </c>
       <c r="C48" t="n">
-        <v>-3.979743719100952</v>
+        <v>-2.062025308609009</v>
       </c>
       <c r="D48" t="n">
-        <v>-4.751028060913086</v>
+        <v>-3.840449333190918</v>
       </c>
       <c r="E48" t="n">
-        <v>-5.068764686584473</v>
+        <v>-2.99256157875061</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t xml:space="preserve">c1ccc2c(c1)cnc3ccccc23 </t>
+          <t>Clc1cccc(c1Cl)c2cccc(Cl)c2Cl</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>-2.779999971389771</v>
+        <v>-7.28000020980835</v>
       </c>
       <c r="C49" t="n">
-        <v>-4.114800930023193</v>
+        <v>-6.655401229858398</v>
       </c>
       <c r="D49" t="n">
-        <v>-3.70870566368103</v>
+        <v>-6.389612197875977</v>
       </c>
       <c r="E49" t="n">
-        <v>-4.155386447906494</v>
+        <v>-6.357316493988037</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>CCCC(=O)OCC</t>
+          <t>CCCC(C)CO</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>-1.360000014305115</v>
+        <v>-1.110000014305115</v>
       </c>
       <c r="C50" t="n">
-        <v>-2.012958765029907</v>
+        <v>-0.6362533569335938</v>
       </c>
       <c r="D50" t="n">
-        <v>-1.092036724090576</v>
+        <v>-1.40971851348877</v>
       </c>
       <c r="E50" t="n">
-        <v>-1.345478534698486</v>
+        <v>-1.57562267780304</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>CC(C)C(C)C(C)C</t>
+          <t>C1c2ccccc2c3ccccc13</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>-4.800000190734863</v>
+        <v>-5</v>
       </c>
       <c r="C51" t="n">
-        <v>-2.988903760910034</v>
+        <v>-4.913756370544434</v>
       </c>
       <c r="D51" t="n">
-        <v>-4.519809246063232</v>
+        <v>-4.893359184265137</v>
       </c>
       <c r="E51" t="n">
-        <v>-4.824079513549805</v>
+        <v>-5.267385959625244</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>CCCCSP(=O)(SCCCC)SCCCC</t>
+          <t xml:space="preserve">Clc1ccc(cc1)c2cc(Cl)ccc2Cl </t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>-5.139999866485596</v>
+        <v>-6.25</v>
       </c>
       <c r="C52" t="n">
-        <v>-3.452996015548706</v>
+        <v>-6.44429349899292</v>
       </c>
       <c r="D52" t="n">
-        <v>-5.296207904815674</v>
+        <v>-6.23479175567627</v>
       </c>
       <c r="E52" t="n">
-        <v>-3.145201921463013</v>
+        <v>-6.374898910522461</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t xml:space="preserve">CC1OC(CC(O)C1O)OC2C(O)CC(OC2C)OC8C(O)CC(OC7CCC3(C)C(CCC4C3CCC5(C)C(CCC45O)C6=CC(=O)OC6)C7)OC8C </t>
+          <t>Clc2ccc1oc(=O)[nH]c1c2</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>-5.293000221252441</v>
+        <v>-2.831000089645386</v>
       </c>
       <c r="C53" t="n">
-        <v>-4.340768814086914</v>
+        <v>-4.378538131713867</v>
       </c>
       <c r="D53" t="n">
-        <v>-3.536198377609253</v>
+        <v>-4.449090003967285</v>
       </c>
       <c r="E53" t="n">
-        <v>-4.517770767211914</v>
+        <v>-4.603055953979492</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>CN(C=Nc1ccc(C)cc1C)C=Nc2ccc(C)cc2C</t>
+          <t>CCN(CC(C)=C)c1c(cc(cc1N(=O)=O)C(F)(F)F)N(=O)=O</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>-5.46999979019165</v>
+        <v>-6.124000072479248</v>
       </c>
       <c r="C54" t="n">
-        <v>-2.78728175163269</v>
+        <v>-5.529722213745117</v>
       </c>
       <c r="D54" t="n">
-        <v>-3.359138011932373</v>
+        <v>-4.342024326324463</v>
       </c>
       <c r="E54" t="n">
-        <v>-3.46190071105957</v>
+        <v>-5.314225196838379</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t xml:space="preserve">CCC1(CCC(=O)NC1=O)c2ccccc2 </t>
+          <t xml:space="preserve">NC(=O)CCl </t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>-2.336999893188477</v>
+        <v>-0.01999999955296516</v>
       </c>
       <c r="C55" t="n">
-        <v>-2.95121693611145</v>
+        <v>-0.370069682598114</v>
       </c>
       <c r="D55" t="n">
-        <v>-1.963773131370544</v>
+        <v>1.024089097976685</v>
       </c>
       <c r="E55" t="n">
-        <v>-2.093295812606812</v>
+        <v>1.022707104682922</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>CCCI</t>
+          <t xml:space="preserve">CCN2c1ccccc1N(C)C(=O)c3cccnc23 </t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>-2.289999961853027</v>
+        <v>-3.323999881744385</v>
       </c>
       <c r="C56" t="n">
-        <v>-2.761032819747925</v>
+        <v>-3.611038446426392</v>
       </c>
       <c r="D56" t="n">
-        <v>-2.387005090713501</v>
+        <v>-3.298320055007935</v>
       </c>
       <c r="E56" t="n">
-        <v>-2.680777549743652</v>
+        <v>-3.820059537887573</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>CC(C)I</t>
+          <t xml:space="preserve">O=C2NC(=O)C1(CCCCCC1)C(=O)N2 </t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>-2.089999914169312</v>
+        <v>-3.167999982833862</v>
       </c>
       <c r="C57" t="n">
-        <v>-3.731343507766724</v>
+        <v>-2.978398561477661</v>
       </c>
       <c r="D57" t="n">
-        <v>-2.388848304748535</v>
+        <v>-2.064072132110596</v>
       </c>
       <c r="E57" t="n">
-        <v>-2.761707305908203</v>
+        <v>-2.43675708770752</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>CC(C)OP(=S)(OC(C)C)SCCNS(=O)(=O)c1ccccc1</t>
+          <t>CCCCCCCI</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>-4.199999809265137</v>
+        <v>-4.809999942779541</v>
       </c>
       <c r="C58" t="n">
-        <v>-3.941599369049072</v>
+        <v>-5.611281394958496</v>
       </c>
       <c r="D58" t="n">
-        <v>-3.592638492584229</v>
+        <v>-4.583449363708496</v>
       </c>
       <c r="E58" t="n">
-        <v>-3.946954727172852</v>
+        <v>-5.018939018249512</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>CCCCO</t>
+          <t>Cc1c(C)c(C)c(C)c(C)c1C</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>0</v>
+        <v>-5.230000019073486</v>
       </c>
       <c r="C59" t="n">
-        <v>-0.9358204007148743</v>
+        <v>-2.358680009841919</v>
       </c>
       <c r="D59" t="n">
-        <v>0.8734091520309448</v>
+        <v>-3.103813648223877</v>
       </c>
       <c r="E59" t="n">
-        <v>0.5761311650276184</v>
+        <v>-3.660740375518799</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t xml:space="preserve">CC(=O)OCC(=O)C3(O)C(CC4C2CCC1=CC(=O)C=CC1(C)C2(F)C(O)CC34C)OC(C)=O </t>
+          <t>OC3N=C(c1ccccc1Cl)c2cc(Cl)ccc2NC3=O</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>-4.130000114440918</v>
+        <v>-3.604000091552734</v>
       </c>
       <c r="C60" t="n">
-        <v>-4.832242488861084</v>
+        <v>-3.512502908706665</v>
       </c>
       <c r="D60" t="n">
-        <v>-3.670135736465454</v>
+        <v>-4.040088176727295</v>
       </c>
       <c r="E60" t="n">
-        <v>-5.381006717681885</v>
+        <v>-4.223285675048828</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>C1CCC2CCCCC2C1</t>
+          <t>Clc1cc(Cl)c(Cl)cc1Cl</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>-5.190000057220459</v>
+        <v>-5.559999942779541</v>
       </c>
       <c r="C61" t="n">
-        <v>-3.524638175964355</v>
+        <v>-5.792505741119385</v>
       </c>
       <c r="D61" t="n">
-        <v>-4.271805763244629</v>
+        <v>-5.077377796173096</v>
       </c>
       <c r="E61" t="n">
-        <v>-4.354333877563477</v>
+        <v>-5.21562671661377</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>CCCCCCC=C</t>
+          <t>Cc1ccc2c(ccc3ccccc32)c1</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>-4.440000057220459</v>
+        <v>-5.840000152587891</v>
       </c>
       <c r="C62" t="n">
-        <v>-5.090243816375732</v>
+        <v>-5.733476638793945</v>
       </c>
       <c r="D62" t="n">
-        <v>-4.421394348144531</v>
+        <v>-5.624702453613281</v>
       </c>
       <c r="E62" t="n">
-        <v>-4.452487468719482</v>
+        <v>-6.221129894256592</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>CCCCCCC#C</t>
+          <t>O=c2[nH]c1CCCc1c(=O)n2C3CCCCC3</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>-3.660000085830688</v>
+        <v>-4.593999862670898</v>
       </c>
       <c r="C63" t="n">
-        <v>-4.289619922637939</v>
+        <v>-2.822067022323608</v>
       </c>
       <c r="D63" t="n">
-        <v>-3.562958002090454</v>
+        <v>-2.551870346069336</v>
       </c>
       <c r="E63" t="n">
-        <v>-3.678079128265381</v>
+        <v>-2.724203824996948</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>CN(C)C(=O)Nc1cccc(c1)C(F)(F)F</t>
+          <t>OC(c1ccc(Cl)cc1)(c2ccc(Cl)cc2)C(Cl)(Cl)Cl</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>-3.430000066757202</v>
+        <v>-5.665999889373779</v>
       </c>
       <c r="C64" t="n">
-        <v>-3.403784036636353</v>
+        <v>-3.337887525558472</v>
       </c>
       <c r="D64" t="n">
-        <v>-2.800993680953979</v>
+        <v>-6.011440753936768</v>
       </c>
       <c r="E64" t="n">
-        <v>-3.096115589141846</v>
+        <v>-5.378460884094238</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>O=C1NC(=O)C(N1)(c2ccccc2)c3ccccc3</t>
+          <t xml:space="preserve">O=c2c(C3CCCc4ccccc43)c(O)c1ccccc1o2 </t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>-4.097000122070312</v>
+        <v>-2.839999914169312</v>
       </c>
       <c r="C65" t="n">
-        <v>-1.398383140563965</v>
+        <v>-4.411759853363037</v>
       </c>
       <c r="D65" t="n">
-        <v>-3.36695122718811</v>
+        <v>-3.440930604934692</v>
       </c>
       <c r="E65" t="n">
-        <v>-3.797734022140503</v>
+        <v>-4.449376583099365</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Cc1cccc2ccccc12</t>
+          <t xml:space="preserve">CCC1(C(=O)NC(=O)NC1=O)C2=CCCCC2 </t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>-3.700000047683716</v>
+        <v>-2.170000076293945</v>
       </c>
       <c r="C66" t="n">
-        <v>-4.200287818908691</v>
+        <v>-2.492186546325684</v>
       </c>
       <c r="D66" t="n">
-        <v>-2.96370005607605</v>
+        <v>-1.624372243881226</v>
       </c>
       <c r="E66" t="n">
-        <v>-3.926556587219238</v>
+        <v>-2.230015277862549</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>CCc1ccc(CC)cc1</t>
+          <t>NS(=O)(=O)c1cc(ccc1Cl)C2(O)NC(=O)c3ccccc23</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>-3.75</v>
+        <v>-3.450999975204468</v>
       </c>
       <c r="C67" t="n">
-        <v>-2.994212627410889</v>
+        <v>-3.862864255905151</v>
       </c>
       <c r="D67" t="n">
-        <v>-2.900886297225952</v>
+        <v>-3.253827333450317</v>
       </c>
       <c r="E67" t="n">
-        <v>-3.380977153778076</v>
+        <v>-4.176395416259766</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t xml:space="preserve">CN(C)C(=O)N(C)C </t>
+          <t xml:space="preserve">Clc1cc(Cl)c(Cl)c(c1Cl)c2c(Cl)c(Cl)cc(Cl)c2Cl </t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>0.9399999976158142</v>
+        <v>-9.149999618530273</v>
       </c>
       <c r="C68" t="n">
-        <v>-0.01325821876525879</v>
+        <v>-10.70015907287598</v>
       </c>
       <c r="D68" t="n">
-        <v>1.331225037574768</v>
+        <v>-9.968945503234863</v>
       </c>
       <c r="E68" t="n">
-        <v>2.212501049041748</v>
+        <v>-10.78099346160889</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Cc1c2ccccc2c(C)c3ccc4ccccc4c13</t>
+          <t xml:space="preserve">Clc1ccc(c(Cl)c1)c2c(Cl)ccc(Cl)c2Cl </t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>-7.019999980926514</v>
+        <v>-7.429999828338623</v>
       </c>
       <c r="C69" t="n">
-        <v>-6.801912307739258</v>
+        <v>-7.238236904144287</v>
       </c>
       <c r="D69" t="n">
-        <v>-5.792720317840576</v>
+        <v>-7.523164749145508</v>
       </c>
       <c r="E69" t="n">
-        <v>-7.044397354125977</v>
+        <v>-7.475503444671631</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t xml:space="preserve">CC(C)OC(=O)C(O)(c1ccc(Br)cc1)c2ccc(Br)cc2 </t>
+          <t xml:space="preserve">ClCCC#N </t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>-4.929999828338623</v>
+        <v>-0.2899999916553497</v>
       </c>
       <c r="C70" t="n">
-        <v>-4.293446063995361</v>
+        <v>-0.05247518420219421</v>
       </c>
       <c r="D70" t="n">
-        <v>-4.455994129180908</v>
+        <v>0.03077012300491333</v>
       </c>
       <c r="E70" t="n">
-        <v>-4.827681541442871</v>
+        <v>-0.03209087997674942</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>CC(C)=CCC/C(C)=C\CO</t>
+          <t xml:space="preserve">CCN2c1nc(C)cc(C)c1NC(=O)c3cccnc23 </t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>-2.460000038146973</v>
+        <v>-4.553999900817871</v>
       </c>
       <c r="C71" t="n">
-        <v>-1.753380298614502</v>
+        <v>-4.34306001663208</v>
       </c>
       <c r="D71" t="n">
-        <v>-1.385920524597168</v>
+        <v>-2.516530752182007</v>
       </c>
       <c r="E71" t="n">
-        <v>-1.740351796150208</v>
+        <v>-3.939096450805664</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>CCOC=O</t>
+          <t>NNc1ccccc1</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>0.1500000059604645</v>
+        <v>0.07000000029802322</v>
       </c>
       <c r="C72" t="n">
-        <v>-0.282507061958313</v>
+        <v>-2.435388803482056</v>
       </c>
       <c r="D72" t="n">
-        <v>0.1821426451206207</v>
+        <v>-1.281317710876465</v>
       </c>
       <c r="E72" t="n">
-        <v>-0.1746558994054794</v>
+        <v>-2.199532032012939</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Cc1ccc(O)cc1</t>
+          <t>CCc1ccccc1CC</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>-0.7300000190734863</v>
+        <v>-3.279999971389771</v>
       </c>
       <c r="C73" t="n">
-        <v>-0.9905171394348145</v>
+        <v>-3.287542104721069</v>
       </c>
       <c r="D73" t="n">
-        <v>-0.9620548486709595</v>
+        <v>-2.755104541778564</v>
       </c>
       <c r="E73" t="n">
-        <v>-1.100190997123718</v>
+        <v>-3.140584707260132</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Cc1ccnc(C)c1</t>
+          <t>COCOC</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>0.3799999952316284</v>
+        <v>0.4799999892711639</v>
       </c>
       <c r="C74" t="n">
-        <v>-2.68199610710144</v>
+        <v>-0.2570478320121765</v>
       </c>
       <c r="D74" t="n">
-        <v>0.4178992807865143</v>
+        <v>1.904172897338867</v>
       </c>
       <c r="E74" t="n">
-        <v>0.2305695563554764</v>
+        <v>1.083474516868591</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t xml:space="preserve">Clc1cc(Cl)c(cc1Cl)c2cccc(Cl)c2Cl </t>
+          <t>CC(C)(C)c1ccccc1</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>-7.210000038146973</v>
+        <v>-3.660000085830688</v>
       </c>
       <c r="C75" t="n">
-        <v>-8.221999168395996</v>
+        <v>-2.646278619766235</v>
       </c>
       <c r="D75" t="n">
-        <v>-7.184834480285645</v>
+        <v>-2.694091081619263</v>
       </c>
       <c r="E75" t="n">
-        <v>-7.304799556732178</v>
+        <v>-2.699716567993164</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t xml:space="preserve">CCc1cccc(C)c1N(C(C)COC)C(=O)CCl </t>
+          <t>CN(C(=O)NC(C)(C)c1ccccc1)c2ccccc2</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>-2.730000019073486</v>
+        <v>-3.349999904632568</v>
       </c>
       <c r="C76" t="n">
-        <v>-2.939491033554077</v>
+        <v>-3.223229646682739</v>
       </c>
       <c r="D76" t="n">
-        <v>-2.125195503234863</v>
+        <v>-3.483408212661743</v>
       </c>
       <c r="E76" t="n">
-        <v>-2.508442878723145</v>
+        <v>-3.459478139877319</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>C1c2ccccc2c3cc4ccccc4cc13</t>
+          <t>CCCCC1(CC)C(=O)NC(=O)NC1=O</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>-8.039999961853027</v>
+        <v>-1.66100001335144</v>
       </c>
       <c r="C77" t="n">
-        <v>-6.027445316314697</v>
+        <v>-2.420048475265503</v>
       </c>
       <c r="D77" t="n">
-        <v>-6.242658138275146</v>
+        <v>-1.711767435073853</v>
       </c>
       <c r="E77" t="n">
-        <v>-6.465671062469482</v>
+        <v>-2.472298860549927</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>COc1cc(CC=C)ccc1O</t>
+          <t>c1(C(C)(C)C)cc(C(C)(C)C)cc(OC(=O)NC)c1</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>-1.559999942779541</v>
+        <v>-4.239999771118164</v>
       </c>
       <c r="C78" t="n">
-        <v>-3.303941965103149</v>
+        <v>-3.857328176498413</v>
       </c>
       <c r="D78" t="n">
-        <v>-2.200674295425415</v>
+        <v>-3.745121240615845</v>
       </c>
       <c r="E78" t="n">
-        <v>-2.509926080703735</v>
+        <v>-4.314848899841309</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>CCC</t>
+          <t>CCCCC(O)CC</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>-1.940000057220459</v>
+        <v>-1.470000028610229</v>
       </c>
       <c r="C79" t="n">
-        <v>-1.842042446136475</v>
+        <v>-1.304957628250122</v>
       </c>
       <c r="D79" t="n">
-        <v>-1.969370722770691</v>
+        <v>-0.9520342350006104</v>
       </c>
       <c r="E79" t="n">
-        <v>-2.562392711639404</v>
+        <v>-1.048635005950928</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>CCCCCCCCC(=O)C</t>
+          <t>Nc1ccc(Cl)cc1</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>-3.299999952316284</v>
+        <v>-1.659999966621399</v>
       </c>
       <c r="C80" t="n">
-        <v>-2.285112380981445</v>
+        <v>-2.011624097824097</v>
       </c>
       <c r="D80" t="n">
-        <v>-3.560709238052368</v>
+        <v>-2.125923156738281</v>
       </c>
       <c r="E80" t="n">
-        <v>-3.656545162200928</v>
+        <v>-1.750833630561829</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>c1ccc2c(c1)c3cccc4c3c2cc5ccccc54</t>
+          <t>CC(=O)Nc1ccccc1</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>-8.229999542236328</v>
+        <v>-1.330000042915344</v>
       </c>
       <c r="C81" t="n">
-        <v>-7.000439643859863</v>
+        <v>-2.317893028259277</v>
       </c>
       <c r="D81" t="n">
-        <v>-7.209824562072754</v>
+        <v>-1.225629806518555</v>
       </c>
       <c r="E81" t="n">
-        <v>-8.354071617126465</v>
+        <v>-1.754204034805298</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>CC(C)C(=O)C(C)C</t>
+          <t xml:space="preserve">CN(C)C(=O)Nc1cccc(OC(=O)NC(C)(C)C)c1 </t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>-1.299999952316284</v>
+        <v>-2.930000066757202</v>
       </c>
       <c r="C82" t="n">
-        <v>-1.550107002258301</v>
+        <v>-4.352286338806152</v>
       </c>
       <c r="D82" t="n">
-        <v>-2.244295597076416</v>
+        <v>-3.325854778289795</v>
       </c>
       <c r="E82" t="n">
-        <v>-0.6186586618423462</v>
+        <v>-4.071657180786133</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Cc1ccncc1C</t>
+          <t>CCCCCCCCCO</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>0.3600000143051147</v>
+        <v>-3.009999990463257</v>
       </c>
       <c r="C83" t="n">
-        <v>-3.176824331283569</v>
+        <v>-4.425107002258301</v>
       </c>
       <c r="D83" t="n">
-        <v>0.2786268293857574</v>
+        <v>-3.440058708190918</v>
       </c>
       <c r="E83" t="n">
-        <v>-0.4873433709144592</v>
+        <v>-3.972935199737549</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t xml:space="preserve">Oc1c(Br)cc(C#N)cc1Br </t>
+          <t>CCOc1ccc(NC(N)=O)cc1</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>-3.329999923706055</v>
+        <v>-2.170000076293945</v>
       </c>
       <c r="C84" t="n">
-        <v>-3.131744623184204</v>
+        <v>-2.077120542526245</v>
       </c>
       <c r="D84" t="n">
-        <v>-2.309514760971069</v>
+        <v>-2.500223159790039</v>
       </c>
       <c r="E84" t="n">
-        <v>-2.570044040679932</v>
+        <v>-2.102227926254272</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>COc1ccc(Cl)cc1</t>
+          <t xml:space="preserve">Cc1c[nH]c2ccccc12 </t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>-2.779999971389771</v>
+        <v>-2.420000076293945</v>
       </c>
       <c r="C85" t="n">
-        <v>-3.155120849609375</v>
+        <v>-1.61547064781189</v>
       </c>
       <c r="D85" t="n">
-        <v>-3.028475761413574</v>
+        <v>-2.770393371582031</v>
       </c>
       <c r="E85" t="n">
-        <v>-2.923956394195557</v>
+        <v>-2.89501428604126</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>OC1CCCCCC1</t>
+          <t>Cc2ncc1nccnc1n2</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>-0.8799999952316284</v>
+        <v>-0.119999997317791</v>
       </c>
       <c r="C86" t="n">
-        <v>-0.8318802118301392</v>
+        <v>-2.123048067092896</v>
       </c>
       <c r="D86" t="n">
-        <v>-0.5739985704421997</v>
+        <v>-0.466023862361908</v>
       </c>
       <c r="E86" t="n">
-        <v>-1.0162034034729</v>
+        <v>-0.9904626607894897</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t xml:space="preserve">CC34CCC1C(CCc2cc(O)ccc12)C3CCC4(O)C#C </t>
+          <t>CCC(C(CC)c1ccc(O)cc1)c2ccc(O)cc2</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>-4.300000190734863</v>
+        <v>-4.429999828338623</v>
       </c>
       <c r="C87" t="n">
-        <v>-5.145263671875</v>
+        <v>-2.036766290664673</v>
       </c>
       <c r="D87" t="n">
-        <v>-4.523312568664551</v>
+        <v>-4.489862442016602</v>
       </c>
       <c r="E87" t="n">
-        <v>-5.764450073242188</v>
+        <v>-4.17534351348877</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>CC(C)CCO</t>
+          <t>CN2C(=O)CN=C(c1ccccc1)c3cc(Cl)ccc23</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>-0.5099999904632568</v>
+        <v>-3.753999948501587</v>
       </c>
       <c r="C88" t="n">
-        <v>-0.8907327651977539</v>
+        <v>-4.121768474578857</v>
       </c>
       <c r="D88" t="n">
-        <v>0.363967090845108</v>
+        <v>-3.388696432113647</v>
       </c>
       <c r="E88" t="n">
-        <v>-0.3425743579864502</v>
+        <v>-3.983532428741455</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>c1cc2ccc3ccc4ccc5ccc6ccc1c7c2c3c4c5c67</t>
+          <t xml:space="preserve">Clc1ccc(cc1)c2c(Cl)cccc2Cl </t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>-9.331999778747559</v>
+        <v>-6.139999866485596</v>
       </c>
       <c r="C89" t="n">
-        <v>-6.718152046203613</v>
+        <v>-6.905728340148926</v>
       </c>
       <c r="D89" t="n">
-        <v>-9.190752029418945</v>
+        <v>-5.872524261474609</v>
       </c>
       <c r="E89" t="n">
-        <v>-9.70618724822998</v>
+        <v>-5.776759147644043</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>COC(=O)c1ccccc1OC2OC(COC3OCC(O)C(O)C3O)C(O)C(O)C2O</t>
+          <t>C=CC=O</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>-0.7419999837875366</v>
+        <v>0.5699999928474426</v>
       </c>
       <c r="C90" t="n">
-        <v>-1.831138849258423</v>
+        <v>-0.7392231822013855</v>
       </c>
       <c r="D90" t="n">
-        <v>-1.743572473526001</v>
+        <v>1.092215538024902</v>
       </c>
       <c r="E90" t="n">
-        <v>-2.389898777008057</v>
+        <v>0.6101822257041931</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>CC(C)C(C)(C)C</t>
+          <t xml:space="preserve">Clc2c(Cl)c(Cl)c(c1ccccc1)c(Cl)c2Cl </t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>-4.360000133514404</v>
+        <v>-7.920000076293945</v>
       </c>
       <c r="C91" t="n">
-        <v>-3.180883169174194</v>
+        <v>-8.719134330749512</v>
       </c>
       <c r="D91" t="n">
-        <v>-3.245185852050781</v>
+        <v>-7.552773475646973</v>
       </c>
       <c r="E91" t="n">
-        <v>-3.784351825714111</v>
+        <v>-7.782117366790771</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Cc1cccc2c(C)cccc12</t>
+          <t xml:space="preserve">CC(C)N(C(=O)CCl)c1ccccc1 </t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>-4.678999900817871</v>
+        <v>-2.480000019073486</v>
       </c>
       <c r="C92" t="n">
-        <v>-4.05644416809082</v>
+        <v>-3.831347703933716</v>
       </c>
       <c r="D92" t="n">
-        <v>-3.317065000534058</v>
+        <v>-2.140496969223022</v>
       </c>
       <c r="E92" t="n">
-        <v>-3.993107318878174</v>
+        <v>-3.372420310974121</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>CCOP(=S)(NC(C)C)Oc1ccccc1C(=O)OC(C)C</t>
+          <t>O=C1N(COC(=O)CCCCCC)C(=O)C(N1)(c2ccccc2)c3ccccc3</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>-4.193999767303467</v>
+        <v>-6.301000118255615</v>
       </c>
       <c r="C93" t="n">
-        <v>-4.810862064361572</v>
+        <v>-6.52747917175293</v>
       </c>
       <c r="D93" t="n">
-        <v>-4.340675354003906</v>
+        <v>-4.808577537536621</v>
       </c>
       <c r="E93" t="n">
-        <v>-4.119688987731934</v>
+        <v>-5.454899787902832</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>COC(=O)Nc1cccc(OC(=O)Nc2cccc(C)c2)c1</t>
+          <t>O=C1N(COC(=O)CCC)C(=O)C(N1)(c2ccccc2)c3ccccc3</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>-4.804999828338623</v>
+        <v>-5.071000099182129</v>
       </c>
       <c r="C94" t="n">
-        <v>-3.46017050743103</v>
+        <v>-5.099422931671143</v>
       </c>
       <c r="D94" t="n">
-        <v>-3.696460008621216</v>
+        <v>-4.737900257110596</v>
       </c>
       <c r="E94" t="n">
-        <v>-4.366849422454834</v>
+        <v>-5.361794471740723</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>CCCCCCCCCC(C)O</t>
+          <t>Cc1cc(=O)[nH]c(=S)[nH]1</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>-2.940000057220459</v>
+        <v>-2.436000108718872</v>
       </c>
       <c r="C95" t="n">
-        <v>-2.413548707962036</v>
+        <v>-1.692938089370728</v>
       </c>
       <c r="D95" t="n">
-        <v>-4.270812511444092</v>
+        <v>-2.216315984725952</v>
       </c>
       <c r="E95" t="n">
-        <v>-4.498041152954102</v>
+        <v>-2.041881799697876</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>CCCOC(=O)CC</t>
+          <t>O=C3CN=C(c1ccccc1)c2cc(ccc2N3)N(=O)=O</t>
         </is>
       </c>
       <c r="B96" t="n">
-        <v>-0.8199999928474426</v>
+        <v>-3.796000003814697</v>
       </c>
       <c r="C96" t="n">
-        <v>-0.7324656248092651</v>
+        <v>-3.564473390579224</v>
       </c>
       <c r="D96" t="n">
-        <v>0.2004177868366241</v>
+        <v>-2.6360764503479</v>
       </c>
       <c r="E96" t="n">
-        <v>-0.6247316598892212</v>
+        <v>-2.838701725006104</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cn1cnc2n(C)c(=O)[nH]c(=O)c12 </t>
+          <t>CCCOC</t>
         </is>
       </c>
       <c r="B97" t="n">
-        <v>-2.523000001907349</v>
+        <v>-0.3899999856948853</v>
       </c>
       <c r="C97" t="n">
-        <v>-0.4056726098060608</v>
+        <v>-1.074516534805298</v>
       </c>
       <c r="D97" t="n">
-        <v>-1.105240225791931</v>
+        <v>-0.03971317410469055</v>
       </c>
       <c r="E97" t="n">
-        <v>-1.7009596824646</v>
+        <v>-0.06127861887216568</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>O=C2NC(=O)C1(CCCCCCC1)C(=O)N2</t>
+          <t xml:space="preserve">CCC(=C(CC)c1ccc(O)cc1)c2ccc(O)cc2 </t>
         </is>
       </c>
       <c r="B98" t="n">
-        <v>-2.982000112533569</v>
+        <v>-4.070000171661377</v>
       </c>
       <c r="C98" t="n">
-        <v>-2.971434354782104</v>
+        <v>-1.348686218261719</v>
       </c>
       <c r="D98" t="n">
-        <v>-1.953007698059082</v>
+        <v>-3.938366651535034</v>
       </c>
       <c r="E98" t="n">
-        <v>-2.517774105072021</v>
+        <v>-3.372622489929199</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>CCCCCCCCCCCC(=O)OC</t>
+          <t>CCC(O)C(C)C</t>
         </is>
       </c>
       <c r="B99" t="n">
-        <v>-4.690000057220459</v>
+        <v>-0.699999988079071</v>
       </c>
       <c r="C99" t="n">
-        <v>-3.796470880508423</v>
+        <v>-1.052579402923584</v>
       </c>
       <c r="D99" t="n">
-        <v>-5.039464950561523</v>
+        <v>-1.030848979949951</v>
       </c>
       <c r="E99" t="n">
-        <v>-5.267027854919434</v>
+        <v>-0.4967425763607025</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Clc1ccc2ccccc2c1</t>
+          <t>C1SC(=S)NC1(=O)</t>
         </is>
       </c>
       <c r="B100" t="n">
-        <v>-4.139999866485596</v>
+        <v>-1.769999980926514</v>
       </c>
       <c r="C100" t="n">
-        <v>-4.17372989654541</v>
+        <v>-2.200832366943359</v>
       </c>
       <c r="D100" t="n">
-        <v>-4.578880786895752</v>
+        <v>-0.4083172678947449</v>
       </c>
       <c r="E100" t="n">
-        <v>-5.105916976928711</v>
+        <v>-1.881846070289612</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Cc2cnc1cncnc1n2</t>
+          <t>CC2(C)C1CCC(C)(C1)C2=O</t>
         </is>
       </c>
       <c r="B101" t="n">
-        <v>-0.8539999723434448</v>
+        <v>-1.850000023841858</v>
       </c>
       <c r="C101" t="n">
-        <v>-1.050473690032959</v>
+        <v>-1.998949527740479</v>
       </c>
       <c r="D101" t="n">
-        <v>0.5837380886077881</v>
+        <v>-3.006075143814087</v>
       </c>
       <c r="E101" t="n">
-        <v>-0.3498328328132629</v>
+        <v>-5.169058322906494</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Brc1ccccc1</t>
+          <t>C</t>
         </is>
       </c>
       <c r="B102" t="n">
-        <v>-2.549999952316284</v>
+        <v>-0.8999999761581421</v>
       </c>
       <c r="C102" t="n">
-        <v>-3.189474105834961</v>
+        <v>-0.927800714969635</v>
       </c>
       <c r="D102" t="n">
-        <v>-2.44513201713562</v>
+        <v>2.805129766464233</v>
       </c>
       <c r="E102" t="n">
-        <v>-2.621275901794434</v>
+        <v>-1.846914410591125</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Fc1cccc(F)c1C(=O)NC(=O)Nc2ccc(Cl)cc2</t>
+          <t>CCCCOC=O</t>
         </is>
       </c>
       <c r="B103" t="n">
-        <v>-6.019999980926514</v>
+        <v>-1.370000004768372</v>
       </c>
       <c r="C103" t="n">
-        <v>-4.201300621032715</v>
+        <v>-0.924373984336853</v>
       </c>
       <c r="D103" t="n">
-        <v>-4.909643650054932</v>
+        <v>-0.7366430163383484</v>
       </c>
       <c r="E103" t="n">
-        <v>-5.555308818817139</v>
+        <v>-0.9577938318252563</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Cc1cccc(c1)N(=O)=O</t>
+          <t>Cc1cc(ccc1NS(=O)(=O)C(F)(F)F)S(=O)(=O)c2ccccc2</t>
         </is>
       </c>
       <c r="B104" t="n">
-        <v>-2.440000057220459</v>
+        <v>-3.799999952316284</v>
       </c>
       <c r="C104" t="n">
-        <v>-2.188262939453125</v>
+        <v>-3.430959463119507</v>
       </c>
       <c r="D104" t="n">
-        <v>-1.510489940643311</v>
+        <v>-3.011582612991333</v>
       </c>
       <c r="E104" t="n">
-        <v>-2.340098857879639</v>
+        <v>-3.828155994415283</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>CCNc1nc(NC(C)C)nc(SC)n1</t>
+          <t>Oc1ccc(Cl)cc1</t>
         </is>
       </c>
       <c r="B105" t="n">
-        <v>-3.039999961853027</v>
+        <v>-0.699999988079071</v>
       </c>
       <c r="C105" t="n">
-        <v>-3.927313566207886</v>
+        <v>-1.046175003051758</v>
       </c>
       <c r="D105" t="n">
-        <v>-3.096064805984497</v>
+        <v>-1.786777019500732</v>
       </c>
       <c r="E105" t="n">
-        <v>-3.170719861984253</v>
+        <v>-1.40218448638916</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nc1nc(O)nc2nc[nH]c12 </t>
+          <t xml:space="preserve">CC(C)C1CCC(C)CC1O </t>
         </is>
       </c>
       <c r="B106" t="n">
-        <v>-3.401000022888184</v>
+        <v>-2.529999971389771</v>
       </c>
       <c r="C106" t="n">
-        <v>-1.669584274291992</v>
+        <v>-3.448181390762329</v>
       </c>
       <c r="D106" t="n">
-        <v>-2.565295457839966</v>
+        <v>-2.403213739395142</v>
       </c>
       <c r="E106" t="n">
-        <v>-2.87169337272644</v>
+        <v>-2.328813314437866</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nc3ccc2cc1ccccc1cc2c3 </t>
+          <t>Nc3nc(N)c2nc(c1ccccc1)c(N)nc2n3</t>
         </is>
       </c>
       <c r="B107" t="n">
-        <v>-5.170000076293945</v>
+        <v>-2.404000043869019</v>
       </c>
       <c r="C107" t="n">
-        <v>-6.859623432159424</v>
+        <v>-3.920103311538696</v>
       </c>
       <c r="D107" t="n">
-        <v>-5.330418109893799</v>
+        <v>-3.348984956741333</v>
       </c>
       <c r="E107" t="n">
-        <v>-5.947095394134521</v>
+        <v>-3.375505924224854</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>C(c1ccccc1)c2ccccc2</t>
+          <t xml:space="preserve">Nc1ncnc2nc[nH]c12 </t>
         </is>
       </c>
       <c r="B108" t="n">
-        <v>-4.079999923706055</v>
+        <v>-2.119999885559082</v>
       </c>
       <c r="C108" t="n">
-        <v>-2.994349718093872</v>
+        <v>-1.815014362335205</v>
       </c>
       <c r="D108" t="n">
-        <v>-3.660028219223022</v>
+        <v>-1.473628282546997</v>
       </c>
       <c r="E108" t="n">
-        <v>-4.17632007598877</v>
+        <v>-1.226570725440979</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>NC(=S)Nc1ccccc1</t>
+          <t>Clc1ccccc1Cl</t>
         </is>
       </c>
       <c r="B109" t="n">
-        <v>-1.769999980926514</v>
+        <v>-3.049999952316284</v>
       </c>
       <c r="C109" t="n">
-        <v>-2.393747568130493</v>
+        <v>-3.282390117645264</v>
       </c>
       <c r="D109" t="n">
-        <v>-2.382059335708618</v>
+        <v>-2.991384029388428</v>
       </c>
       <c r="E109" t="n">
-        <v>-2.701718807220459</v>
+        <v>-3.058705806732178</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Clc1ccc(c(Cl)c1)c2c(Cl)c(Cl)c(Cl)c(Cl)c2Cl</t>
+          <t>CCCCS</t>
         </is>
       </c>
       <c r="B110" t="n">
-        <v>-7.920000076293945</v>
+        <v>-2.180000066757202</v>
       </c>
       <c r="C110" t="n">
-        <v>-8.896871566772461</v>
+        <v>-2.072874307632446</v>
       </c>
       <c r="D110" t="n">
-        <v>-8.833114624023438</v>
+        <v>-1.87795090675354</v>
       </c>
       <c r="E110" t="n">
-        <v>-9.161283493041992</v>
+        <v>-1.616225719451904</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t xml:space="preserve">Clc1ccc(Cl)c(c1)c2c(Cl)c(Cl)cc(Cl)c2Cl </t>
+          <t>Cc1cc(C)c2ccccc2c1</t>
         </is>
       </c>
       <c r="B111" t="n">
-        <v>-7.420000076293945</v>
+        <v>-4.289999961853027</v>
       </c>
       <c r="C111" t="n">
-        <v>-8.747114181518555</v>
+        <v>-5.06313943862915</v>
       </c>
       <c r="D111" t="n">
-        <v>-8.476469993591309</v>
+        <v>-3.6840980052948</v>
       </c>
       <c r="E111" t="n">
-        <v>-8.950307846069336</v>
+        <v>-4.280255317687988</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>ClCC#CCOC(=O)Nc1cccc(Cl)c1</t>
+          <t>CCC(C)Cl</t>
         </is>
       </c>
       <c r="B112" t="n">
-        <v>-4.369999885559082</v>
+        <v>-1.960000038146973</v>
       </c>
       <c r="C112" t="n">
-        <v>-1.640316009521484</v>
+        <v>-1.713338613510132</v>
       </c>
       <c r="D112" t="n">
-        <v>-2.836534023284912</v>
+        <v>-1.740782260894775</v>
       </c>
       <c r="E112" t="n">
-        <v>-4.066117763519287</v>
+        <v>-1.973912954330444</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>CCCCC(CC)COC(=O)c1ccccc1C(=O)OCC(CC)CCCC</t>
+          <t xml:space="preserve">Cc3ccnc4N(C1CC1)c2ncccc2C(=O)Nc34 </t>
         </is>
       </c>
       <c r="B113" t="n">
-        <v>-6.960000038146973</v>
+        <v>-3.190000057220459</v>
       </c>
       <c r="C113" t="n">
-        <v>-4.786139965057373</v>
+        <v>-5.158430099487305</v>
       </c>
       <c r="D113" t="n">
-        <v>-4.741176128387451</v>
+        <v>-2.819785118103027</v>
       </c>
       <c r="E113" t="n">
-        <v>-4.807557582855225</v>
+        <v>-4.808247566223145</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>CC(=O)C1(O)CCC2C3CCC4=CC(=O)CCC4(C)C3CCC21C</t>
+          <t>COC(=O)c1ccccc1</t>
         </is>
       </c>
       <c r="B114" t="n">
-        <v>-3.816999912261963</v>
+        <v>-1.850000023841858</v>
       </c>
       <c r="C114" t="n">
-        <v>-3.883710861206055</v>
+        <v>-1.836837291717529</v>
       </c>
       <c r="D114" t="n">
-        <v>-3.559011459350586</v>
+        <v>-1.365636587142944</v>
       </c>
       <c r="E114" t="n">
-        <v>-3.983210802078247</v>
+        <v>-1.626354932785034</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
+          <t>CC(C)Br</t>
+        </is>
+      </c>
+      <c r="B115" t="n">
+        <v>-1.590000033378601</v>
+      </c>
+      <c r="C115" t="n">
+        <v>-1.273884534835815</v>
+      </c>
+      <c r="D115" t="n">
+        <v>-2.44351601600647</v>
+      </c>
+      <c r="E115" t="n">
+        <v>-0.6930594444274902</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>C=CCCC=C</t>
+        </is>
+      </c>
+      <c r="B116" t="n">
+        <v>-2.680000066757202</v>
+      </c>
+      <c r="C116" t="n">
+        <v>-2.27535343170166</v>
+      </c>
+      <c r="D116" t="n">
+        <v>-2.588549375534058</v>
+      </c>
+      <c r="E116" t="n">
+        <v>-2.678702831268311</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>CN(C)C(=O)Nc1ccc(Cl)c(Cl)c1</t>
+        </is>
+      </c>
+      <c r="B117" t="n">
+        <v>-3.799999952316284</v>
+      </c>
+      <c r="C117" t="n">
+        <v>-3.18061351776123</v>
+      </c>
+      <c r="D117" t="n">
+        <v>-3.031132459640503</v>
+      </c>
+      <c r="E117" t="n">
+        <v>-3.553382396697998</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>O=C1NC(=O)NC(=O)C1(CC=C)c1ccccc1</t>
+        </is>
+      </c>
+      <c r="B118" t="n">
+        <v>-2.36899995803833</v>
+      </c>
+      <c r="C118" t="n">
+        <v>-1.925285816192627</v>
+      </c>
+      <c r="D118" t="n">
+        <v>-1.840515375137329</v>
+      </c>
+      <c r="E118" t="n">
+        <v>-2.228986501693726</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NS(=O)(=O)c2cc1c(NC(NS1(=O)=O)C(Cl)Cl)cc2Cl </t>
+        </is>
+      </c>
+      <c r="B119" t="n">
+        <v>-2.680000066757202</v>
+      </c>
+      <c r="C119" t="n">
+        <v>-4.398379802703857</v>
+      </c>
+      <c r="D119" t="n">
+        <v>-3.118659734725952</v>
+      </c>
+      <c r="E119" t="n">
+        <v>-2.666866779327393</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>ClCc1ccccc1</t>
+        </is>
+      </c>
+      <c r="B120" t="n">
+        <v>-2.390000104904175</v>
+      </c>
+      <c r="C120" t="n">
+        <v>-3.246140241622925</v>
+      </c>
+      <c r="D120" t="n">
+        <v>-2.596175909042358</v>
+      </c>
+      <c r="E120" t="n">
+        <v>-2.322214365005493</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>C/C=C/C=O</t>
+        </is>
+      </c>
+      <c r="B121" t="n">
+        <v>0.3199999928474426</v>
+      </c>
+      <c r="C121" t="n">
+        <v>-0.7571551203727722</v>
+      </c>
+      <c r="D121" t="n">
+        <v>1.073553323745728</v>
+      </c>
+      <c r="E121" t="n">
+        <v>0.3280182778835297</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>CCC#CCC</t>
+        </is>
+      </c>
+      <c r="B122" t="n">
+        <v>-1.990000009536743</v>
+      </c>
+      <c r="C122" t="n">
+        <v>-1.672264814376831</v>
+      </c>
+      <c r="D122" t="n">
+        <v>1.220817089080811</v>
+      </c>
+      <c r="E122" t="n">
+        <v>-1.362870454788208</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CCCCc1c(C)nc(NCC)nc1OS(=O)(=O)N(C)C </t>
+        </is>
+      </c>
+      <c r="B123" t="n">
+        <v>-4.159999847412109</v>
+      </c>
+      <c r="C123" t="n">
+        <v>-2.670006990432739</v>
+      </c>
+      <c r="D123" t="n">
+        <v>-2.995450258255005</v>
+      </c>
+      <c r="E123" t="n">
+        <v>-3.376078128814697</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>CC(C)CC(=O)C</t>
+        </is>
+      </c>
+      <c r="B124" t="n">
+        <v>-0.7400000095367432</v>
+      </c>
+      <c r="C124" t="n">
+        <v>-0.767941951751709</v>
+      </c>
+      <c r="D124" t="n">
+        <v>-0.4164691567420959</v>
+      </c>
+      <c r="E124" t="n">
+        <v>-0.8107441663742065</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>O=C1NC(=O)NC(=O)C1(CC)C(C)C</t>
+        </is>
+      </c>
+      <c r="B125" t="n">
+        <v>-2.148000001907349</v>
+      </c>
+      <c r="C125" t="n">
+        <v>-2.237829923629761</v>
+      </c>
+      <c r="D125" t="n">
+        <v>-1.361948490142822</v>
+      </c>
+      <c r="E125" t="n">
+        <v>-2.339643955230713</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>CC(C)C</t>
+        </is>
+      </c>
+      <c r="B126" t="n">
+        <v>-2.549999952316284</v>
+      </c>
+      <c r="C126" t="n">
+        <v>-1.042532205581665</v>
+      </c>
+      <c r="D126" t="n">
+        <v>-2.89517879486084</v>
+      </c>
+      <c r="E126" t="n">
+        <v>-3.17542576789856</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>O=N(=O)c1c(Cl)c(Cl)ccc1</t>
+        </is>
+      </c>
+      <c r="B127" t="n">
+        <v>-3.480000019073486</v>
+      </c>
+      <c r="C127" t="n">
+        <v>-3.010205984115601</v>
+      </c>
+      <c r="D127" t="n">
+        <v>-2.918776273727417</v>
+      </c>
+      <c r="E127" t="n">
+        <v>-3.146713972091675</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CC5(C)OC4CC3C2CCC1=CC(=O)C=CC1(C)C2(F)C(O)CC3(C)C4(O5)C(=O)CO </t>
+        </is>
+      </c>
+      <c r="B128" t="n">
+        <v>-4.309999942779541</v>
+      </c>
+      <c r="C128" t="n">
+        <v>-2.562120914459229</v>
+      </c>
+      <c r="D128" t="n">
+        <v>-3.111007928848267</v>
+      </c>
+      <c r="E128" t="n">
+        <v>-3.133038520812988</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CC34CC(O)C1(F)C(CCC2=CC(=O)CCC12C)C3CCC4(O)C(=O)CO </t>
+        </is>
+      </c>
+      <c r="B129" t="n">
+        <v>-3.430000066757202</v>
+      </c>
+      <c r="C129" t="n">
+        <v>-3.590538263320923</v>
+      </c>
+      <c r="D129" t="n">
+        <v>-2.975078344345093</v>
+      </c>
+      <c r="E129" t="n">
+        <v>-3.263823986053467</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>CC(C)O</t>
+        </is>
+      </c>
+      <c r="B130" t="n">
+        <v>0.4300000071525574</v>
+      </c>
+      <c r="C130" t="n">
+        <v>0.02519845962524414</v>
+      </c>
+      <c r="D130" t="n">
+        <v>1.406975269317627</v>
+      </c>
+      <c r="E130" t="n">
+        <v>1.443897008895874</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>O=C(c1ccccc1)c2ccccc2</t>
+        </is>
+      </c>
+      <c r="B131" t="n">
+        <v>-3.119999885559082</v>
+      </c>
+      <c r="C131" t="n">
+        <v>-1.234200954437256</v>
+      </c>
+      <c r="D131" t="n">
+        <v>-2.291321754455566</v>
+      </c>
+      <c r="E131" t="n">
+        <v>-2.82435131072998</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>CC(C)(C)C(=O)C(Oc1ccc(Cl)cc1)n2cncn2</t>
+        </is>
+      </c>
+      <c r="B132" t="n">
+        <v>-3.609999895095825</v>
+      </c>
+      <c r="C132" t="n">
+        <v>-1.88230037689209</v>
+      </c>
+      <c r="D132" t="n">
+        <v>-4.128632545471191</v>
+      </c>
+      <c r="E132" t="n">
+        <v>-3.95619535446167</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>CCCN(CCC)c1c(cc(cc1N(=O)=O)C(F)(F)F)N(=O)=O</t>
+        </is>
+      </c>
+      <c r="B133" t="n">
+        <v>-5.679999828338623</v>
+      </c>
+      <c r="C133" t="n">
+        <v>-6.014980316162109</v>
+      </c>
+      <c r="D133" t="n">
+        <v>-5.203518867492676</v>
+      </c>
+      <c r="E133" t="n">
+        <v>-6.357968330383301</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>Oc1ccc(Br)cc1</t>
+        </is>
+      </c>
+      <c r="B134" t="n">
+        <v>-1.090000033378601</v>
+      </c>
+      <c r="C134" t="n">
+        <v>-1.286911487579346</v>
+      </c>
+      <c r="D134" t="n">
+        <v>-1.645604133605957</v>
+      </c>
+      <c r="E134" t="n">
+        <v>-1.526905179023743</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>c1ccc2c(c1)cc3ccc4cccc5ccc2c3c45</t>
+        </is>
+      </c>
+      <c r="B135" t="n">
+        <v>-8.699000358581543</v>
+      </c>
+      <c r="C135" t="n">
+        <v>-7.762458801269531</v>
+      </c>
+      <c r="D135" t="n">
+        <v>-7.471595764160156</v>
+      </c>
+      <c r="E135" t="n">
+        <v>-8.111312866210938</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>COc1ccccc1Cl</t>
+        </is>
+      </c>
+      <c r="B136" t="n">
+        <v>-2.460000038146973</v>
+      </c>
+      <c r="C136" t="n">
+        <v>-3.195137739181519</v>
+      </c>
+      <c r="D136" t="n">
+        <v>-1.891895294189453</v>
+      </c>
+      <c r="E136" t="n">
+        <v>-2.217450857162476</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>CCCCCCCCC=C</t>
+        </is>
+      </c>
+      <c r="B137" t="n">
+        <v>-5.510000228881836</v>
+      </c>
+      <c r="C137" t="n">
+        <v>-4.945281028747559</v>
+      </c>
+      <c r="D137" t="n">
+        <v>-5.232598304748535</v>
+      </c>
+      <c r="E137" t="n">
+        <v>-5.486766815185547</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>CCNc1ccccc1</t>
+        </is>
+      </c>
+      <c r="B138" t="n">
+        <v>-1.700000047683716</v>
+      </c>
+      <c r="C138" t="n">
+        <v>-1.685100555419922</v>
+      </c>
+      <c r="D138" t="n">
+        <v>-1.854490280151367</v>
+      </c>
+      <c r="E138" t="n">
+        <v>-2.129405736923218</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>Cc1ccccc1Br</t>
+        </is>
+      </c>
+      <c r="B139" t="n">
+        <v>-2.230000019073486</v>
+      </c>
+      <c r="C139" t="n">
+        <v>-3.091370344161987</v>
+      </c>
+      <c r="D139" t="n">
+        <v>-3.038296461105347</v>
+      </c>
+      <c r="E139" t="n">
+        <v>-2.626920461654663</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>CCCOC(C)C</t>
+        </is>
+      </c>
+      <c r="B140" t="n">
+        <v>-1.340000033378601</v>
+      </c>
+      <c r="C140" t="n">
+        <v>-1.286738157272339</v>
+      </c>
+      <c r="D140" t="n">
+        <v>-1.364502191543579</v>
+      </c>
+      <c r="E140" t="n">
+        <v>-1.809064388275146</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>CCCCC(CC)C=O</t>
+        </is>
+      </c>
+      <c r="B141" t="n">
+        <v>-2.130000114440918</v>
+      </c>
+      <c r="C141" t="n">
+        <v>-3.075000524520874</v>
+      </c>
+      <c r="D141" t="n">
+        <v>-2.250136375427246</v>
+      </c>
+      <c r="E141" t="n">
+        <v>-2.29794979095459</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>BrCCBr</t>
+        </is>
+      </c>
+      <c r="B142" t="n">
+        <v>-1.679999947547913</v>
+      </c>
+      <c r="C142" t="n">
+        <v>-0.9920716285705566</v>
+      </c>
+      <c r="D142" t="n">
+        <v>-0.9843719601631165</v>
+      </c>
+      <c r="E142" t="n">
+        <v>-1.259189605712891</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OCC3OC(OCC2OC(OC(C#N)c1ccccc1)C(O)C(O)C2O)C(O)C(O)C3O </t>
+        </is>
+      </c>
+      <c r="B143" t="n">
+        <v>-0.7699999809265137</v>
+      </c>
+      <c r="C143" t="n">
+        <v>-1.160461664199829</v>
+      </c>
+      <c r="D143" t="n">
+        <v>-2.22425389289856</v>
+      </c>
+      <c r="E143" t="n">
+        <v>-3.996167659759521</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>CCCCCl</t>
+        </is>
+      </c>
+      <c r="B144" t="n">
+        <v>-2.029999971389771</v>
+      </c>
+      <c r="C144" t="n">
+        <v>-1.981315135955811</v>
+      </c>
+      <c r="D144" t="n">
+        <v>-2.065371990203857</v>
+      </c>
+      <c r="E144" t="n">
+        <v>-1.788842678070068</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>O=N(=O)c1cc(cc(c1)N(=O)=O)N(=O)=O</t>
+        </is>
+      </c>
+      <c r="B145" t="n">
+        <v>-2.890000104904175</v>
+      </c>
+      <c r="C145" t="n">
+        <v>-3.172745943069458</v>
+      </c>
+      <c r="D145" t="n">
+        <v>-2.026519775390625</v>
+      </c>
+      <c r="E145" t="n">
+        <v>-2.000531911849976</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CC1=C(CCCO1)C(=O)Nc2ccccc2 </t>
+        </is>
+      </c>
+      <c r="B146" t="n">
+        <v>-2.559999942779541</v>
+      </c>
+      <c r="C146" t="n">
+        <v>-2.697423219680786</v>
+      </c>
+      <c r="D146" t="n">
+        <v>-2.574907064437866</v>
+      </c>
+      <c r="E146" t="n">
+        <v>-3.973390102386475</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>CCCC1COC(Cn2cncn2)(O1)c3ccc(Cl)cc3Cl</t>
+        </is>
+      </c>
+      <c r="B147" t="n">
+        <v>-3.493000030517578</v>
+      </c>
+      <c r="C147" t="n">
+        <v>-4.438587665557861</v>
+      </c>
+      <c r="D147" t="n">
+        <v>-2.24622654914856</v>
+      </c>
+      <c r="E147" t="n">
+        <v>-2.943714618682861</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>Cc1cccc(C)c1</t>
+        </is>
+      </c>
+      <c r="B148" t="n">
+        <v>-2.819999933242798</v>
+      </c>
+      <c r="C148" t="n">
+        <v>-3.35469388961792</v>
+      </c>
+      <c r="D148" t="n">
+        <v>-1.961756229400635</v>
+      </c>
+      <c r="E148" t="n">
+        <v>-2.461005449295044</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>CCCCCCCl</t>
+        </is>
+      </c>
+      <c r="B149" t="n">
+        <v>-3.119999885559082</v>
+      </c>
+      <c r="C149" t="n">
+        <v>-3.973251104354858</v>
+      </c>
+      <c r="D149" t="n">
+        <v>-3.291593313217163</v>
+      </c>
+      <c r="E149" t="n">
+        <v>-3.641382217407227</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>CCCCC(=O)OCC</t>
+        </is>
+      </c>
+      <c r="B150" t="n">
+        <v>-2.25</v>
+      </c>
+      <c r="C150" t="n">
+        <v>-1.932415246963501</v>
+      </c>
+      <c r="D150" t="n">
+        <v>-1.415889739990234</v>
+      </c>
+      <c r="E150" t="n">
+        <v>-1.612942099571228</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>CC34CCc1c(ccc2cc(O)ccc12)C3CCC4=O</t>
+        </is>
+      </c>
+      <c r="B151" t="n">
+        <v>-5.239999771118164</v>
+      </c>
+      <c r="C151" t="n">
+        <v>-2.665804386138916</v>
+      </c>
+      <c r="D151" t="n">
+        <v>-4.275213241577148</v>
+      </c>
+      <c r="E151" t="n">
+        <v>-5.008925437927246</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t xml:space="preserve">COc2cc1c(N)nc(nc1c(OC)c2OC)N3CCN(CC3)C(=O)OCC(C)(C)O </t>
+        </is>
+      </c>
+      <c r="B152" t="n">
+        <v>-3.638000011444092</v>
+      </c>
+      <c r="C152" t="n">
+        <v>-3.165543794631958</v>
+      </c>
+      <c r="D152" t="n">
+        <v>-1.771007299423218</v>
+      </c>
+      <c r="E152" t="n">
+        <v>-2.352121353149414</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t xml:space="preserve">COc1ncnc2nccnc12 </t>
+        </is>
+      </c>
+      <c r="B153" t="n">
+        <v>-1.110000014305115</v>
+      </c>
+      <c r="C153" t="n">
+        <v>-0.7352296710014343</v>
+      </c>
+      <c r="D153" t="n">
+        <v>-0.8245241045951843</v>
+      </c>
+      <c r="E153" t="n">
+        <v>-0.3274101912975311</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>Cc1ccc(C)c(C)c1</t>
+        </is>
+      </c>
+      <c r="B154" t="n">
+        <v>-3.309999942779541</v>
+      </c>
+      <c r="C154" t="n">
+        <v>-3.677719116210938</v>
+      </c>
+      <c r="D154" t="n">
+        <v>-2.848449945449829</v>
+      </c>
+      <c r="E154" t="n">
+        <v>-3.295403957366943</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>CCOC(=O)CC</t>
+        </is>
+      </c>
+      <c r="B155" t="n">
+        <v>-0.6600000262260437</v>
+      </c>
+      <c r="C155" t="n">
+        <v>-0.5640267133712769</v>
+      </c>
+      <c r="D155" t="n">
+        <v>0.4531031250953674</v>
+      </c>
+      <c r="E155" t="n">
+        <v>0.1714358627796173</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t xml:space="preserve">O2c1ccc(N)cc1N(C)C(=O)c3cc(C)ccc23 </t>
+        </is>
+      </c>
+      <c r="B156" t="n">
+        <v>-3.927999973297119</v>
+      </c>
+      <c r="C156" t="n">
+        <v>-2.29908013343811</v>
+      </c>
+      <c r="D156" t="n">
+        <v>-2.954238891601562</v>
+      </c>
+      <c r="E156" t="n">
+        <v>-3.616804122924805</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CC4CC3C2CCC1=CC(=O)C=CC1(C)C2(F)C(O)CC3(C)C4(O)C(=O)COC(C)=O </t>
+        </is>
+      </c>
+      <c r="B157" t="n">
+        <v>-4.900000095367432</v>
+      </c>
+      <c r="C157" t="n">
+        <v>-4.248325347900391</v>
+      </c>
+      <c r="D157" t="n">
+        <v>-3.947291612625122</v>
+      </c>
+      <c r="E157" t="n">
+        <v>-4.984915733337402</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>c1ccccc1n2ncc(N)c(Br)c2(=O)</t>
+        </is>
+      </c>
+      <c r="B158" t="n">
+        <v>-3.127000093460083</v>
+      </c>
+      <c r="C158" t="n">
+        <v>-1.723415851593018</v>
+      </c>
+      <c r="D158" t="n">
+        <v>-2.048310518264771</v>
+      </c>
+      <c r="E158" t="n">
+        <v>-2.653112173080444</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>Oc1ccc(Cl)cc1C(=O)Nc2ccc(cc2Cl)N(=O)=O</t>
+        </is>
+      </c>
+      <c r="B159" t="n">
+        <v>-4.699999809265137</v>
+      </c>
+      <c r="C159" t="n">
+        <v>-4.719100952148438</v>
+      </c>
+      <c r="D159" t="n">
+        <v>-4.898316383361816</v>
+      </c>
+      <c r="E159" t="n">
+        <v>-5.487009048461914</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t xml:space="preserve">c1ccc2c(c1)cnc3ccccc23 </t>
+        </is>
+      </c>
+      <c r="B160" t="n">
+        <v>-2.779999971389771</v>
+      </c>
+      <c r="C160" t="n">
+        <v>-4.084736347198486</v>
+      </c>
+      <c r="D160" t="n">
+        <v>-4.221806049346924</v>
+      </c>
+      <c r="E160" t="n">
+        <v>-3.940428256988525</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>CCCC(=O)OCC</t>
+        </is>
+      </c>
+      <c r="B161" t="n">
+        <v>-1.360000014305115</v>
+      </c>
+      <c r="C161" t="n">
+        <v>-1.962586402893066</v>
+      </c>
+      <c r="D161" t="n">
+        <v>-1.310056447982788</v>
+      </c>
+      <c r="E161" t="n">
+        <v>-1.361365437507629</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>CC(C)C(C)C(C)C</t>
+        </is>
+      </c>
+      <c r="B162" t="n">
+        <v>-4.800000190734863</v>
+      </c>
+      <c r="C162" t="n">
+        <v>-3.274721145629883</v>
+      </c>
+      <c r="D162" t="n">
+        <v>-4.176653861999512</v>
+      </c>
+      <c r="E162" t="n">
+        <v>-3.550119638442993</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>CCCCSP(=O)(SCCCC)SCCCC</t>
+        </is>
+      </c>
+      <c r="B163" t="n">
+        <v>-5.139999866485596</v>
+      </c>
+      <c r="C163" t="n">
+        <v>-2.755142450332642</v>
+      </c>
+      <c r="D163" t="n">
+        <v>-5.154512405395508</v>
+      </c>
+      <c r="E163" t="n">
+        <v>-4.238223552703857</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CC1OC(CC(O)C1O)OC2C(O)CC(OC2C)OC8C(O)CC(OC7CCC3(C)C(CCC4C3CCC5(C)C(CCC45O)C6=CC(=O)OC6)C7)OC8C </t>
+        </is>
+      </c>
+      <c r="B164" t="n">
+        <v>-5.293000221252441</v>
+      </c>
+      <c r="C164" t="n">
+        <v>-4.20298433303833</v>
+      </c>
+      <c r="D164" t="n">
+        <v>-3.782090902328491</v>
+      </c>
+      <c r="E164" t="n">
+        <v>-4.237740516662598</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>CN(C=Nc1ccc(C)cc1C)C=Nc2ccc(C)cc2C</t>
+        </is>
+      </c>
+      <c r="B165" t="n">
+        <v>-5.46999979019165</v>
+      </c>
+      <c r="C165" t="n">
+        <v>-2.716846942901611</v>
+      </c>
+      <c r="D165" t="n">
+        <v>-3.653623342514038</v>
+      </c>
+      <c r="E165" t="n">
+        <v>-4.283904075622559</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CCC1(CCC(=O)NC1=O)c2ccccc2 </t>
+        </is>
+      </c>
+      <c r="B166" t="n">
+        <v>-2.336999893188477</v>
+      </c>
+      <c r="C166" t="n">
+        <v>-2.872283697128296</v>
+      </c>
+      <c r="D166" t="n">
+        <v>-1.978184461593628</v>
+      </c>
+      <c r="E166" t="n">
+        <v>-2.048704862594604</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>CCCI</t>
+        </is>
+      </c>
+      <c r="B167" t="n">
+        <v>-2.289999961853027</v>
+      </c>
+      <c r="C167" t="n">
+        <v>-2.344454288482666</v>
+      </c>
+      <c r="D167" t="n">
+        <v>-1.987929105758667</v>
+      </c>
+      <c r="E167" t="n">
+        <v>-2.607591152191162</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>CC(C)I</t>
+        </is>
+      </c>
+      <c r="B168" t="n">
+        <v>-2.089999914169312</v>
+      </c>
+      <c r="C168" t="n">
+        <v>-3.398428678512573</v>
+      </c>
+      <c r="D168" t="n">
+        <v>-3.145911931991577</v>
+      </c>
+      <c r="E168" t="n">
+        <v>-1.940747380256653</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>CC(C)OP(=S)(OC(C)C)SCCNS(=O)(=O)c1ccccc1</t>
+        </is>
+      </c>
+      <c r="B169" t="n">
+        <v>-4.199999809265137</v>
+      </c>
+      <c r="C169" t="n">
+        <v>-3.888888597488403</v>
+      </c>
+      <c r="D169" t="n">
+        <v>-3.371211051940918</v>
+      </c>
+      <c r="E169" t="n">
+        <v>-4.116775035858154</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>CCCCO</t>
+        </is>
+      </c>
+      <c r="B170" t="n">
+        <v>0</v>
+      </c>
+      <c r="C170" t="n">
+        <v>-0.4252352714538574</v>
+      </c>
+      <c r="D170" t="n">
+        <v>0.9359847903251648</v>
+      </c>
+      <c r="E170" t="n">
+        <v>0.5412521362304688</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CC(=O)OCC(=O)C3(O)C(CC4C2CCC1=CC(=O)C=CC1(C)C2(F)C(O)CC34C)OC(C)=O </t>
+        </is>
+      </c>
+      <c r="B171" t="n">
+        <v>-4.130000114440918</v>
+      </c>
+      <c r="C171" t="n">
+        <v>-4.630104064941406</v>
+      </c>
+      <c r="D171" t="n">
+        <v>-3.744206428527832</v>
+      </c>
+      <c r="E171" t="n">
+        <v>-4.826469421386719</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>C1CCC2CCCCC2C1</t>
+        </is>
+      </c>
+      <c r="B172" t="n">
+        <v>-5.190000057220459</v>
+      </c>
+      <c r="C172" t="n">
+        <v>-3.682109355926514</v>
+      </c>
+      <c r="D172" t="n">
+        <v>-4.656093597412109</v>
+      </c>
+      <c r="E172" t="n">
+        <v>-4.17908763885498</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>CCCCCCC=C</t>
+        </is>
+      </c>
+      <c r="B173" t="n">
+        <v>-4.440000057220459</v>
+      </c>
+      <c r="C173" t="n">
+        <v>-4.945281028747559</v>
+      </c>
+      <c r="D173" t="n">
+        <v>-4.202695846557617</v>
+      </c>
+      <c r="E173" t="n">
+        <v>-4.33861255645752</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>CCCCCCC#C</t>
+        </is>
+      </c>
+      <c r="B174" t="n">
+        <v>-3.660000085830688</v>
+      </c>
+      <c r="C174" t="n">
+        <v>-4.17408561706543</v>
+      </c>
+      <c r="D174" t="n">
+        <v>-3.363572597503662</v>
+      </c>
+      <c r="E174" t="n">
+        <v>-3.741205215454102</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>CN(C)C(=O)Nc1cccc(c1)C(F)(F)F</t>
+        </is>
+      </c>
+      <c r="B175" t="n">
+        <v>-3.430000066757202</v>
+      </c>
+      <c r="C175" t="n">
+        <v>-2.84299373626709</v>
+      </c>
+      <c r="D175" t="n">
+        <v>-2.533661127090454</v>
+      </c>
+      <c r="E175" t="n">
+        <v>-2.939850330352783</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>O=C1NC(=O)C(N1)(c2ccccc2)c3ccccc3</t>
+        </is>
+      </c>
+      <c r="B176" t="n">
+        <v>-4.097000122070312</v>
+      </c>
+      <c r="C176" t="n">
+        <v>-1.759236335754395</v>
+      </c>
+      <c r="D176" t="n">
+        <v>-3.563354253768921</v>
+      </c>
+      <c r="E176" t="n">
+        <v>-4.739217758178711</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>Cc1cccc2ccccc12</t>
+        </is>
+      </c>
+      <c r="B177" t="n">
+        <v>-3.700000047683716</v>
+      </c>
+      <c r="C177" t="n">
+        <v>-4.100897312164307</v>
+      </c>
+      <c r="D177" t="n">
+        <v>-3.364634990692139</v>
+      </c>
+      <c r="E177" t="n">
+        <v>-3.874672651290894</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>CCc1ccc(CC)cc1</t>
+        </is>
+      </c>
+      <c r="B178" t="n">
+        <v>-3.75</v>
+      </c>
+      <c r="C178" t="n">
+        <v>-3.226002931594849</v>
+      </c>
+      <c r="D178" t="n">
+        <v>-3.49345874786377</v>
+      </c>
+      <c r="E178" t="n">
+        <v>-3.555415153503418</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CN(C)C(=O)N(C)C </t>
+        </is>
+      </c>
+      <c r="B179" t="n">
+        <v>0.9399999976158142</v>
+      </c>
+      <c r="C179" t="n">
+        <v>-0.1145572662353516</v>
+      </c>
+      <c r="D179" t="n">
+        <v>1.619030714035034</v>
+      </c>
+      <c r="E179" t="n">
+        <v>1.14790141582489</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>Cc1c2ccccc2c(C)c3ccc4ccccc4c13</t>
+        </is>
+      </c>
+      <c r="B180" t="n">
+        <v>-7.019999980926514</v>
+      </c>
+      <c r="C180" t="n">
+        <v>-6.671237945556641</v>
+      </c>
+      <c r="D180" t="n">
+        <v>-6.090344429016113</v>
+      </c>
+      <c r="E180" t="n">
+        <v>-7.093774795532227</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CC(C)OC(=O)C(O)(c1ccc(Br)cc1)c2ccc(Br)cc2 </t>
+        </is>
+      </c>
+      <c r="B181" t="n">
+        <v>-4.929999828338623</v>
+      </c>
+      <c r="C181" t="n">
+        <v>-4.448989868164062</v>
+      </c>
+      <c r="D181" t="n">
+        <v>-4.415549278259277</v>
+      </c>
+      <c r="E181" t="n">
+        <v>-4.786901473999023</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>CC(C)=CCC/C(C)=C\CO</t>
+        </is>
+      </c>
+      <c r="B182" t="n">
+        <v>-2.460000038146973</v>
+      </c>
+      <c r="C182" t="n">
+        <v>-1.673997640609741</v>
+      </c>
+      <c r="D182" t="n">
+        <v>-0.9799109101295471</v>
+      </c>
+      <c r="E182" t="n">
+        <v>-1.063837766647339</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>CCOC=O</t>
+        </is>
+      </c>
+      <c r="B183" t="n">
+        <v>0.1500000059604645</v>
+      </c>
+      <c r="C183" t="n">
+        <v>-0.1227685213088989</v>
+      </c>
+      <c r="D183" t="n">
+        <v>0.1717947125434875</v>
+      </c>
+      <c r="E183" t="n">
+        <v>0.3609411418437958</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>Cc1ccc(O)cc1</t>
+        </is>
+      </c>
+      <c r="B184" t="n">
+        <v>-0.7300000190734863</v>
+      </c>
+      <c r="C184" t="n">
+        <v>-1.009370088577271</v>
+      </c>
+      <c r="D184" t="n">
+        <v>-0.7583237290382385</v>
+      </c>
+      <c r="E184" t="n">
+        <v>-0.7148269414901733</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>Cc1ccnc(C)c1</t>
+        </is>
+      </c>
+      <c r="B185" t="n">
+        <v>0.3799999952316284</v>
+      </c>
+      <c r="C185" t="n">
+        <v>-2.553488254547119</v>
+      </c>
+      <c r="D185" t="n">
+        <v>0.4268454909324646</v>
+      </c>
+      <c r="E185" t="n">
+        <v>0.75147944688797</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Clc1cc(Cl)c(cc1Cl)c2cccc(Cl)c2Cl </t>
+        </is>
+      </c>
+      <c r="B186" t="n">
+        <v>-7.210000038146973</v>
+      </c>
+      <c r="C186" t="n">
+        <v>-7.715540409088135</v>
+      </c>
+      <c r="D186" t="n">
+        <v>-7.235600471496582</v>
+      </c>
+      <c r="E186" t="n">
+        <v>-7.384981632232666</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CCc1cccc(C)c1N(C(C)COC)C(=O)CCl </t>
+        </is>
+      </c>
+      <c r="B187" t="n">
+        <v>-2.730000019073486</v>
+      </c>
+      <c r="C187" t="n">
+        <v>-3.105911493301392</v>
+      </c>
+      <c r="D187" t="n">
+        <v>-2.168435335159302</v>
+      </c>
+      <c r="E187" t="n">
+        <v>-2.178927421569824</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>C1c2ccccc2c3cc4ccccc4cc13</t>
+        </is>
+      </c>
+      <c r="B188" t="n">
+        <v>-8.039999961853027</v>
+      </c>
+      <c r="C188" t="n">
+        <v>-5.756336212158203</v>
+      </c>
+      <c r="D188" t="n">
+        <v>-6.587110042572021</v>
+      </c>
+      <c r="E188" t="n">
+        <v>-6.718892097473145</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>COc1cc(CC=C)ccc1O</t>
+        </is>
+      </c>
+      <c r="B189" t="n">
+        <v>-1.559999942779541</v>
+      </c>
+      <c r="C189" t="n">
+        <v>-2.839235067367554</v>
+      </c>
+      <c r="D189" t="n">
+        <v>-2.166622161865234</v>
+      </c>
+      <c r="E189" t="n">
+        <v>-2.61847710609436</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>CCC</t>
+        </is>
+      </c>
+      <c r="B190" t="n">
+        <v>-1.940000057220459</v>
+      </c>
+      <c r="C190" t="n">
+        <v>-1.296399354934692</v>
+      </c>
+      <c r="D190" t="n">
+        <v>-1.667716264724731</v>
+      </c>
+      <c r="E190" t="n">
+        <v>-2.215542793273926</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>CCCCCCCCC(=O)C</t>
+        </is>
+      </c>
+      <c r="B191" t="n">
+        <v>-3.299999952316284</v>
+      </c>
+      <c r="C191" t="n">
+        <v>-2.232702255249023</v>
+      </c>
+      <c r="D191" t="n">
+        <v>-3.148987054824829</v>
+      </c>
+      <c r="E191" t="n">
+        <v>-3.675707817077637</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>c1ccc2c(c1)c3cccc4c3c2cc5ccccc54</t>
+        </is>
+      </c>
+      <c r="B192" t="n">
+        <v>-8.229999542236328</v>
+      </c>
+      <c r="C192" t="n">
+        <v>-7.17719841003418</v>
+      </c>
+      <c r="D192" t="n">
+        <v>-7.629236221313477</v>
+      </c>
+      <c r="E192" t="n">
+        <v>-8.076272964477539</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>CC(C)C(=O)C(C)C</t>
+        </is>
+      </c>
+      <c r="B193" t="n">
+        <v>-1.299999952316284</v>
+      </c>
+      <c r="C193" t="n">
+        <v>-1.02287232875824</v>
+      </c>
+      <c r="D193" t="n">
+        <v>-1.972144842147827</v>
+      </c>
+      <c r="E193" t="n">
+        <v>-1.635097861289978</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>Cc1ccncc1C</t>
+        </is>
+      </c>
+      <c r="B194" t="n">
+        <v>0.3600000143051147</v>
+      </c>
+      <c r="C194" t="n">
+        <v>-2.653227806091309</v>
+      </c>
+      <c r="D194" t="n">
+        <v>0.3287881016731262</v>
+      </c>
+      <c r="E194" t="n">
+        <v>-0.3056789338588715</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Oc1c(Br)cc(C#N)cc1Br </t>
+        </is>
+      </c>
+      <c r="B195" t="n">
+        <v>-3.329999923706055</v>
+      </c>
+      <c r="C195" t="n">
+        <v>-2.396184206008911</v>
+      </c>
+      <c r="D195" t="n">
+        <v>-2.206686019897461</v>
+      </c>
+      <c r="E195" t="n">
+        <v>-3.073588609695435</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>COc1ccc(Cl)cc1</t>
+        </is>
+      </c>
+      <c r="B196" t="n">
+        <v>-2.779999971389771</v>
+      </c>
+      <c r="C196" t="n">
+        <v>-2.713579893112183</v>
+      </c>
+      <c r="D196" t="n">
+        <v>-3.208815097808838</v>
+      </c>
+      <c r="E196" t="n">
+        <v>-3.11624002456665</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>OC1CCCCCC1</t>
+        </is>
+      </c>
+      <c r="B197" t="n">
+        <v>-0.8799999952316284</v>
+      </c>
+      <c r="C197" t="n">
+        <v>-0.8218758106231689</v>
+      </c>
+      <c r="D197" t="n">
+        <v>-0.5959676504135132</v>
+      </c>
+      <c r="E197" t="n">
+        <v>-0.9562921524047852</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CC34CCC1C(CCc2cc(O)ccc12)C3CCC4(O)C#C </t>
+        </is>
+      </c>
+      <c r="B198" t="n">
+        <v>-4.300000190734863</v>
+      </c>
+      <c r="C198" t="n">
+        <v>-5.607726573944092</v>
+      </c>
+      <c r="D198" t="n">
+        <v>-4.634809017181396</v>
+      </c>
+      <c r="E198" t="n">
+        <v>-5.772545337677002</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>CC(C)CCO</t>
+        </is>
+      </c>
+      <c r="B199" t="n">
+        <v>-0.5099999904632568</v>
+      </c>
+      <c r="C199" t="n">
+        <v>-0.818458080291748</v>
+      </c>
+      <c r="D199" t="n">
+        <v>0.3591498136520386</v>
+      </c>
+      <c r="E199" t="n">
+        <v>-0.2473319470882416</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>c1cc2ccc3ccc4ccc5ccc6ccc1c7c2c3c4c5c67</t>
+        </is>
+      </c>
+      <c r="B200" t="n">
+        <v>-9.331999778747559</v>
+      </c>
+      <c r="C200" t="n">
+        <v>-7.70761775970459</v>
+      </c>
+      <c r="D200" t="n">
+        <v>-9.501126289367676</v>
+      </c>
+      <c r="E200" t="n">
+        <v>-10.12761116027832</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>COC(=O)c1ccccc1OC2OC(COC3OCC(O)C(O)C3O)C(O)C(O)C2O</t>
+        </is>
+      </c>
+      <c r="B201" t="n">
+        <v>-0.7419999837875366</v>
+      </c>
+      <c r="C201" t="n">
+        <v>-2.160424947738647</v>
+      </c>
+      <c r="D201" t="n">
+        <v>-1.671964406967163</v>
+      </c>
+      <c r="E201" t="n">
+        <v>-1.899017453193665</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>CC(C)C(C)(C)C</t>
+        </is>
+      </c>
+      <c r="B202" t="n">
+        <v>-4.360000133514404</v>
+      </c>
+      <c r="C202" t="n">
+        <v>-3.379376649856567</v>
+      </c>
+      <c r="D202" t="n">
+        <v>-2.971911430358887</v>
+      </c>
+      <c r="E202" t="n">
+        <v>-3.572522163391113</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>Cc1cccc2c(C)cccc12</t>
+        </is>
+      </c>
+      <c r="B203" t="n">
+        <v>-4.678999900817871</v>
+      </c>
+      <c r="C203" t="n">
+        <v>-4.162530422210693</v>
+      </c>
+      <c r="D203" t="n">
+        <v>-3.667237043380737</v>
+      </c>
+      <c r="E203" t="n">
+        <v>-4.021686553955078</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>CCOP(=S)(NC(C)C)Oc1ccccc1C(=O)OC(C)C</t>
+        </is>
+      </c>
+      <c r="B204" t="n">
+        <v>-4.193999767303467</v>
+      </c>
+      <c r="C204" t="n">
+        <v>-4.936203956604004</v>
+      </c>
+      <c r="D204" t="n">
+        <v>-4.029499530792236</v>
+      </c>
+      <c r="E204" t="n">
+        <v>-4.959325790405273</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>COC(=O)Nc1cccc(OC(=O)Nc2cccc(C)c2)c1</t>
+        </is>
+      </c>
+      <c r="B205" t="n">
+        <v>-4.804999828338623</v>
+      </c>
+      <c r="C205" t="n">
+        <v>-3.02837610244751</v>
+      </c>
+      <c r="D205" t="n">
+        <v>-3.707631826400757</v>
+      </c>
+      <c r="E205" t="n">
+        <v>-3.978051662445068</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>CCCCCCCCCC(C)O</t>
+        </is>
+      </c>
+      <c r="B206" t="n">
+        <v>-2.940000057220459</v>
+      </c>
+      <c r="C206" t="n">
+        <v>-2.342364549636841</v>
+      </c>
+      <c r="D206" t="n">
+        <v>-3.873021364212036</v>
+      </c>
+      <c r="E206" t="n">
+        <v>-4.378530025482178</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>CCCOC(=O)CC</t>
+        </is>
+      </c>
+      <c r="B207" t="n">
+        <v>-0.8199999928474426</v>
+      </c>
+      <c r="C207" t="n">
+        <v>-0.6271029710769653</v>
+      </c>
+      <c r="D207" t="n">
+        <v>-0.04161933064460754</v>
+      </c>
+      <c r="E207" t="n">
+        <v>-0.2994782030582428</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cn1cnc2n(C)c(=O)[nH]c(=O)c12 </t>
+        </is>
+      </c>
+      <c r="B208" t="n">
+        <v>-2.523000001907349</v>
+      </c>
+      <c r="C208" t="n">
+        <v>-0.5631662607192993</v>
+      </c>
+      <c r="D208" t="n">
+        <v>-0.6279786229133606</v>
+      </c>
+      <c r="E208" t="n">
+        <v>-1.677920818328857</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>O=C2NC(=O)C1(CCCCCCC1)C(=O)N2</t>
+        </is>
+      </c>
+      <c r="B209" t="n">
+        <v>-2.982000112533569</v>
+      </c>
+      <c r="C209" t="n">
+        <v>-2.978398561477661</v>
+      </c>
+      <c r="D209" t="n">
+        <v>-2.124951362609863</v>
+      </c>
+      <c r="E209" t="n">
+        <v>-2.489399909973145</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>CCCCCCCCCCCC(=O)OC</t>
+        </is>
+      </c>
+      <c r="B210" t="n">
+        <v>-4.690000057220459</v>
+      </c>
+      <c r="C210" t="n">
+        <v>-3.588441610336304</v>
+      </c>
+      <c r="D210" t="n">
+        <v>-4.659186840057373</v>
+      </c>
+      <c r="E210" t="n">
+        <v>-5.156670570373535</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>Clc1ccc2ccccc2c1</t>
+        </is>
+      </c>
+      <c r="B211" t="n">
+        <v>-4.139999866485596</v>
+      </c>
+      <c r="C211" t="n">
+        <v>-5.060987949371338</v>
+      </c>
+      <c r="D211" t="n">
+        <v>-4.948045253753662</v>
+      </c>
+      <c r="E211" t="n">
+        <v>-5.228131771087646</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>Cc2cnc1cncnc1n2</t>
+        </is>
+      </c>
+      <c r="B212" t="n">
+        <v>-0.8539999723434448</v>
+      </c>
+      <c r="C212" t="n">
+        <v>-0.8181026577949524</v>
+      </c>
+      <c r="D212" t="n">
+        <v>0.435229480266571</v>
+      </c>
+      <c r="E212" t="n">
+        <v>0.1742148697376251</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>Brc1ccccc1</t>
+        </is>
+      </c>
+      <c r="B213" t="n">
+        <v>-2.549999952316284</v>
+      </c>
+      <c r="C213" t="n">
+        <v>-3.076022386550903</v>
+      </c>
+      <c r="D213" t="n">
+        <v>-2.715204954147339</v>
+      </c>
+      <c r="E213" t="n">
+        <v>-2.752111434936523</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>Fc1cccc(F)c1C(=O)NC(=O)Nc2ccc(Cl)cc2</t>
+        </is>
+      </c>
+      <c r="B214" t="n">
+        <v>-6.019999980926514</v>
+      </c>
+      <c r="C214" t="n">
+        <v>-2.931064367294312</v>
+      </c>
+      <c r="D214" t="n">
+        <v>-5.16630744934082</v>
+      </c>
+      <c r="E214" t="n">
+        <v>-5.843255996704102</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>Cc1cccc(c1)N(=O)=O</t>
+        </is>
+      </c>
+      <c r="B215" t="n">
+        <v>-2.440000057220459</v>
+      </c>
+      <c r="C215" t="n">
+        <v>-2.772315979003906</v>
+      </c>
+      <c r="D215" t="n">
+        <v>-1.73504376411438</v>
+      </c>
+      <c r="E215" t="n">
+        <v>-2.195192813873291</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>CCNc1nc(NC(C)C)nc(SC)n1</t>
+        </is>
+      </c>
+      <c r="B216" t="n">
+        <v>-3.039999961853027</v>
+      </c>
+      <c r="C216" t="n">
+        <v>-3.963171243667603</v>
+      </c>
+      <c r="D216" t="n">
+        <v>-2.955140590667725</v>
+      </c>
+      <c r="E216" t="n">
+        <v>-3.450321674346924</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Nc1nc(O)nc2nc[nH]c12 </t>
+        </is>
+      </c>
+      <c r="B217" t="n">
+        <v>-3.401000022888184</v>
+      </c>
+      <c r="C217" t="n">
+        <v>-2.256106853485107</v>
+      </c>
+      <c r="D217" t="n">
+        <v>-2.518840074539185</v>
+      </c>
+      <c r="E217" t="n">
+        <v>-3.709043025970459</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Nc3ccc2cc1ccccc1cc2c3 </t>
+        </is>
+      </c>
+      <c r="B218" t="n">
+        <v>-5.170000076293945</v>
+      </c>
+      <c r="C218" t="n">
+        <v>-5.949832916259766</v>
+      </c>
+      <c r="D218" t="n">
+        <v>-5.46418285369873</v>
+      </c>
+      <c r="E218" t="n">
+        <v>-6.101224899291992</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>C(c1ccccc1)c2ccccc2</t>
+        </is>
+      </c>
+      <c r="B219" t="n">
+        <v>-4.079999923706055</v>
+      </c>
+      <c r="C219" t="n">
+        <v>-2.879827260971069</v>
+      </c>
+      <c r="D219" t="n">
+        <v>-3.922612428665161</v>
+      </c>
+      <c r="E219" t="n">
+        <v>-3.884416103363037</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>NC(=S)Nc1ccccc1</t>
+        </is>
+      </c>
+      <c r="B220" t="n">
+        <v>-1.769999980926514</v>
+      </c>
+      <c r="C220" t="n">
+        <v>-2.162791728973389</v>
+      </c>
+      <c r="D220" t="n">
+        <v>-1.803005456924438</v>
+      </c>
+      <c r="E220" t="n">
+        <v>-2.368746042251587</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>Clc1ccc(c(Cl)c1)c2c(Cl)c(Cl)c(Cl)c(Cl)c2Cl</t>
+        </is>
+      </c>
+      <c r="B221" t="n">
+        <v>-7.920000076293945</v>
+      </c>
+      <c r="C221" t="n">
+        <v>-8.714223861694336</v>
+      </c>
+      <c r="D221" t="n">
+        <v>-8.931296348571777</v>
+      </c>
+      <c r="E221" t="n">
+        <v>-8.919175148010254</v>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Clc1ccc(Cl)c(c1)c2c(Cl)c(Cl)cc(Cl)c2Cl </t>
+        </is>
+      </c>
+      <c r="B222" t="n">
+        <v>-7.420000076293945</v>
+      </c>
+      <c r="C222" t="n">
+        <v>-8.584518432617188</v>
+      </c>
+      <c r="D222" t="n">
+        <v>-8.497153282165527</v>
+      </c>
+      <c r="E222" t="n">
+        <v>-8.910359382629395</v>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>ClCC#CCOC(=O)Nc1cccc(Cl)c1</t>
+        </is>
+      </c>
+      <c r="B223" t="n">
+        <v>-4.369999885559082</v>
+      </c>
+      <c r="C223" t="n">
+        <v>-2.294639587402344</v>
+      </c>
+      <c r="D223" t="n">
+        <v>-3.276146650314331</v>
+      </c>
+      <c r="E223" t="n">
+        <v>-3.291757583618164</v>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>CCCCC(CC)COC(=O)c1ccccc1C(=O)OCC(CC)CCCC</t>
+        </is>
+      </c>
+      <c r="B224" t="n">
+        <v>-6.960000038146973</v>
+      </c>
+      <c r="C224" t="n">
+        <v>-3.429763555526733</v>
+      </c>
+      <c r="D224" t="n">
+        <v>-4.612377166748047</v>
+      </c>
+      <c r="E224" t="n">
+        <v>-4.710107326507568</v>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>CC(=O)C1(O)CCC2C3CCC4=CC(=O)CCC4(C)C3CCC21C</t>
+        </is>
+      </c>
+      <c r="B225" t="n">
+        <v>-3.816999912261963</v>
+      </c>
+      <c r="C225" t="n">
+        <v>-4.051911354064941</v>
+      </c>
+      <c r="D225" t="n">
+        <v>-3.619064092636108</v>
+      </c>
+      <c r="E225" t="n">
+        <v>-4.254064083099365</v>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
           <t>CCBr</t>
         </is>
       </c>
-      <c r="B115" t="n">
+      <c r="B226" t="n">
         <v>-1.090000033378601</v>
       </c>
-      <c r="C115" t="n">
-        <v>-1.514193058013916</v>
-      </c>
-      <c r="D115" t="n">
-        <v>-1.289628744125366</v>
-      </c>
-      <c r="E115" t="n">
-        <v>-1.05754554271698</v>
+      <c r="C226" t="n">
+        <v>-1.511445760726929</v>
+      </c>
+      <c r="D226" t="n">
+        <v>-1.323803663253784</v>
+      </c>
+      <c r="E226" t="n">
+        <v>-0.7779959440231323</v>
       </c>
     </row>
   </sheetData>
